--- a/eval_report.xlsx
+++ b/eval_report.xlsx
@@ -1077,6 +1077,56 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5334000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5334000" cy="3810000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1369,7 +1419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X37"/>
+  <dimension ref="A1:X39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1592,7 +1642,7 @@
         <v>-0.0014</v>
       </c>
       <c r="V2" s="5" t="n">
-        <v>623.8200000000001</v>
+        <v>332.17</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>87.09999999999999</v>
@@ -1672,7 +1722,7 @@
         <v>-0.0005</v>
       </c>
       <c r="V3" s="5" t="n">
-        <v>469.04</v>
+        <v>331.42</v>
       </c>
       <c r="W3" s="3" t="n">
         <v>91.8</v>
@@ -1752,7 +1802,7 @@
         <v>-0.0007</v>
       </c>
       <c r="V4" s="5" t="n">
-        <v>335.3</v>
+        <v>371.77</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>88.5</v>
@@ -1832,7 +1882,7 @@
         <v>0.1256</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>362.15</v>
+        <v>256.86</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>96.59999999999999</v>
@@ -1912,7 +1962,7 @@
         <v>0.1049</v>
       </c>
       <c r="V6" s="5" t="n">
-        <v>519.98</v>
+        <v>409.89</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>92</v>
@@ -1992,7 +2042,7 @@
         <v>-0.0026</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>329.88</v>
+        <v>348.16</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>89.7</v>
@@ -2072,7 +2122,7 @@
         <v>0.0307</v>
       </c>
       <c r="V8" s="5" t="n">
-        <v>285.52</v>
+        <v>439.11</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>86.3</v>
@@ -2152,7 +2202,7 @@
         <v>0.0483</v>
       </c>
       <c r="V9" s="5" t="n">
-        <v>291.59</v>
+        <v>444.53</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>93.90000000000001</v>
@@ -2232,7 +2282,7 @@
         <v>0.0872</v>
       </c>
       <c r="V10" s="5" t="n">
-        <v>385.14</v>
+        <v>273.67</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>97.3</v>
@@ -2312,7 +2362,7 @@
         <v>0.0438</v>
       </c>
       <c r="V11" s="5" t="n">
-        <v>402.49</v>
+        <v>425.73</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>95.3</v>
@@ -2392,7 +2442,7 @@
         <v>0.049</v>
       </c>
       <c r="V12" s="5" t="n">
-        <v>399.7</v>
+        <v>428.54</v>
       </c>
       <c r="W12" s="3" t="n">
         <v>94.90000000000001</v>
@@ -2472,7 +2522,7 @@
         <v>0.06950000000000001</v>
       </c>
       <c r="V13" s="5" t="n">
-        <v>361.02</v>
+        <v>361.53</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>93.09999999999999</v>
@@ -2484,12 +2534,12 @@
     <row r="14" ht="300" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C1-ST</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>kaggle_fresh_stale_all_frozen_resnet18</t>
+          <t>kaggle_fresh_stale_all_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2498,78 +2548,78 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>83.2</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>11.8</v>
+        <v>13.8</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>83.3</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>11.7</v>
+        <v>13.7</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>83.2</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>11.7</v>
+        <v>13.8</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="N14" s="4" t="n">
         <v>83.2</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v>0.899</v>
+        <v>13.8</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0.9409999999999999</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0.664</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>0.235</v>
+        <v>0.277</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>0.9862</v>
-      </c>
-      <c r="T14" s="4" t="n">
-        <v>0.8881</v>
+        <v>0.9953</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>0.9441000000000001</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.0512</v>
       </c>
       <c r="V14" s="5" t="n">
-        <v>474.84</v>
+        <v>502.89</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="X14" s="5" t="n">
-        <v>87.90000000000001</v>
+        <v>91.7</v>
+      </c>
+      <c r="X14" s="4" t="n">
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="15" ht="300" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-R18-C1-ST</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>kaggle_fresh_stale_all_head_frozen_resnet18</t>
+          <t>kaggle_fresh_stale_all_frozen_resnet18</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2578,78 +2628,78 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>83.2</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>14.8</v>
+        <v>11.8</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>83.3</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>14.7</v>
+        <v>11.7</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>98</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>83.2</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>14.8</v>
+        <v>11.7</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="N15" s="4" t="n">
         <v>83.2</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>0.96</v>
+        <v>11.8</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>0.899</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0.664</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>0.296</v>
+        <v>0.235</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>0.998</v>
+        <v>0.9862</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.8951</v>
+        <v>0.8881</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>0.1029</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="V15" s="5" t="n">
-        <v>368.93</v>
+        <v>476.71</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>95.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>76.8</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="16" ht="300" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>OWN-R18-C4-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_head_layer4_resnet18</t>
+          <t>kaggle_fresh_stale_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2657,79 +2707,79 @@
           <t>state</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
-        <v>88.90000000000001</v>
+      <c r="D16" s="3" t="n">
+        <v>98</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>83.2</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>88.90000000000001</v>
+        <v>14.8</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>98</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>83.3</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>89</v>
+        <v>14.7</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>98</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>83.2</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>88.90000000000001</v>
+        <v>14.8</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>98</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>83.2</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>0.789</v>
+        <v>14.8</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0.96</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0.664</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>0.125</v>
+        <v>0.296</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.9514</v>
+        <v>0.998</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.8741</v>
+        <v>0.8951</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.1029</v>
       </c>
       <c r="V16" s="5" t="n">
-        <v>429.45</v>
-      </c>
-      <c r="W16" s="4" t="n">
-        <v>87.7</v>
+        <v>260.52</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>95.7</v>
       </c>
       <c r="X16" s="5" t="n">
-        <v>88.09999999999999</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="17" ht="300" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>OWN-EB0-C1-ST</t>
+          <t>OWN-R18-C4-ST</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_frozen_efficientnet_b0</t>
+          <t>kaggle_fruits_quality_all_head_layer4_resnet18</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2738,78 +2788,78 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>84.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>82.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1.8</v>
+        <v>5.7</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>84.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>83.3</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>84.7</v>
+        <v>89</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>84.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0.3</v>
+        <v>5.8</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>84.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>82.5</v>
+        <v>83.2</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>2.2</v>
+        <v>5.7</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0.695</v>
+        <v>0.789</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>0.669</v>
+        <v>0.664</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>0.026</v>
+        <v>0.125</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>0.9182</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>0.951</v>
+        <v>0.9514</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>0.8741</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>-0.0328</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="V17" s="5" t="n">
-        <v>328.35</v>
+        <v>344.09</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>89.59999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>79</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="18" ht="300" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-EB0-C1-ST</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_head_frozen_resnet18</t>
+          <t>kaggle_fruits_quality_all_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -2818,78 +2868,78 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>86</v>
+        <v>84.7</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>83.3</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>87.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>82.5</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.732</v>
+        <v>0.695</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0.669</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>0.063</v>
+        <v>0.026</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.9329</v>
-      </c>
-      <c r="T18" s="4" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.9182</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>0.951</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>0.1007</v>
+        <v>-0.0328</v>
       </c>
       <c r="V18" s="5" t="n">
-        <v>335.32</v>
+        <v>370.7</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>89.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X18" s="5" t="n">
-        <v>89.09999999999999</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" ht="300" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_quality_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2897,79 +2947,79 @@
           <t>state</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
-        <v>91.5</v>
+      <c r="D19" s="4" t="n">
+        <v>86</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>91.5</v>
+        <v>3.1</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="H19" s="4" t="n">
         <v>83.3</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>2.8</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>87.09999999999999</v>
       </c>
       <c r="K19" s="4" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>91.7</v>
+        <v>2.7</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>82.5</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v>0.843</v>
+        <v>3.6</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0.732</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0.669</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>0.174</v>
+        <v>0.063</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>0.973</v>
+        <v>0.9329</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.8881</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>0.0849</v>
+        <v>0.1007</v>
       </c>
       <c r="V19" s="5" t="n">
-        <v>380.33</v>
+        <v>357.29</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>84.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="20" ht="300" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>OWN-EB0-C3-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_head_frozen_efficientnet_b0</t>
+          <t>mendeley_fruits_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2978,78 +3028,78 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>98.7</v>
+        <v>91.5</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>15.8</v>
+        <v>8.6</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>98.7</v>
+        <v>91.5</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>83.3</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>98.7</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>14.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>98.7</v>
+        <v>91.7</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>82.5</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>0.975</v>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>0.843</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0.669</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>0.306</v>
+        <v>0.174</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.9989</v>
-      </c>
-      <c r="T20" s="3" t="n">
-        <v>0.958</v>
+        <v>0.973</v>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>0.8881</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>0.0409</v>
+        <v>0.0849</v>
       </c>
       <c r="V20" s="5" t="n">
-        <v>324.19</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>98.2</v>
+        <v>407.64</v>
+      </c>
+      <c r="W20" s="4" t="n">
+        <v>88.59999999999999</v>
       </c>
       <c r="X20" s="5" t="n">
-        <v>91.5</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="21" ht="300" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C3-ST</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_frozen_resnet18</t>
+          <t>mendeley_lemon_varieties_all_head_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3058,78 +3108,78 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>79.09999999999999</v>
+        <v>98.7</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>82.90000000000001</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>18.5</v>
+        <v>15.8</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>79.2</v>
+        <v>98.7</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>83.3</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>18.4</v>
+        <v>15.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>79.2</v>
+        <v>98.7</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>84.40000000000001</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>18.3</v>
+        <v>14.3</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>97.7</v>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v>79.40000000000001</v>
+        <v>98.7</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>82.5</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>18.3</v>
+        <v>16.2</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.952</v>
+        <v>0.975</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>0.585</v>
+        <v>0.669</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>0.367</v>
+        <v>0.306</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>0.9969</v>
-      </c>
-      <c r="T21" s="4" t="n">
-        <v>0.8462</v>
+        <v>0.9989</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>0.958</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>0.1507</v>
+        <v>0.0409</v>
       </c>
       <c r="V21" s="5" t="n">
-        <v>350.7</v>
+        <v>330.89</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>96.2</v>
+        <v>98.2</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>85</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="22" ht="300" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-R18-C1-ST</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_fresh_rotten_all_frozen_resnet18</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3137,79 +3187,79 @@
           <t>state</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n">
-        <v>86.09999999999999</v>
+      <c r="D22" s="3" t="n">
+        <v>97.59999999999999</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>18.5</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>97.59999999999999</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>79.2</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>86.59999999999999</v>
+        <v>18.4</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>97.5</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>79.2</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>18.3</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>97.7</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>0.732</v>
+        <v>18.3</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.952</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>0.585</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="S22" s="4" t="n">
-        <v>0.8889</v>
-      </c>
-      <c r="T22" s="3" t="n">
-        <v>0.9091</v>
+        <v>0.367</v>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>0.9969</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>0.8462</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>-0.0202</v>
+        <v>0.1507</v>
       </c>
       <c r="V22" s="5" t="n">
-        <v>332.3</v>
-      </c>
-      <c r="W22" s="4" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="X22" s="4" t="n">
-        <v>73.8</v>
+        <v>343.39</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="X22" s="5" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="23" ht="300" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>OWN-R18-C2-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>kaggle_fresh_stale_all_layer4_resnet18</t>
+          <t>kaggle_fruits_quality_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3217,79 +3267,79 @@
           <t>state</t>
         </is>
       </c>
-      <c r="D23" s="3" t="n">
-        <v>98.90000000000001</v>
+      <c r="D23" s="4" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>78.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>7</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>79.2</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>98.8</v>
+        <v>6.9</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>86.59999999999999</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>7.4</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>78.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>0.978</v>
+        <v>6.7</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>0.732</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>0.58</v>
+        <v>0.585</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v>0.9994</v>
-      </c>
-      <c r="T23" s="4" t="n">
-        <v>0.8811</v>
+        <v>0.147</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>0.8889</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>0.9091</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>0.1183</v>
+        <v>-0.0202</v>
       </c>
       <c r="V23" s="5" t="n">
-        <v>396.21</v>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="X23" s="5" t="n">
-        <v>81.2</v>
+        <v>367.21</v>
+      </c>
+      <c r="W23" s="4" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="X23" s="4" t="n">
+        <v>73.8</v>
       </c>
     </row>
     <row r="24" ht="300" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-R18-C2-ST</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_head_frozen_resnet18</t>
+          <t>kaggle_fresh_stale_all_layer4_resnet18</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3298,78 +3348,78 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>78.8</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>20.6</v>
+        <v>20.1</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>79.2</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>20.2</v>
+        <v>19.7</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>79.3</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="N24" s="5" t="n">
         <v>78.7</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>20.7</v>
+        <v>20.2</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.987</v>
+        <v>0.978</v>
       </c>
       <c r="Q24" s="5" t="n">
         <v>0.58</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>0.407</v>
+        <v>0.398</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>0.9994</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8811</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>0.1672</v>
+        <v>0.1183</v>
       </c>
       <c r="V24" s="5" t="n">
-        <v>519.6</v>
+        <v>308.36</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>97.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="X24" s="5" t="n">
-        <v>89.40000000000001</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="25" ht="300" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>OWN-EB0-C4-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_head_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_fresh_rotten_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3377,79 +3427,79 @@
           <t>state</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
-        <v>86.09999999999999</v>
+      <c r="D25" s="3" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>78.8</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>20.6</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>79.2</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>86.59999999999999</v>
+        <v>20.2</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>99.3</v>
       </c>
       <c r="K25" s="5" t="n">
         <v>79.3</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>20</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="N25" s="5" t="n">
         <v>78.7</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="P25" s="5" t="n">
-        <v>0.727</v>
+        <v>20.7</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0.987</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>0.58</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="S25" s="4" t="n">
-        <v>0.8827</v>
+        <v>0.407</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>0.9994</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.8671</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>0.0156</v>
+        <v>0.1672</v>
       </c>
       <c r="V25" s="5" t="n">
-        <v>382.52</v>
-      </c>
-      <c r="W25" s="4" t="n">
+        <v>421.72</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="X25" s="5" t="n">
         <v>89.40000000000001</v>
-      </c>
-      <c r="X25" s="5" t="n">
-        <v>84</v>
       </c>
     </row>
     <row r="26" ht="300" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-EB0-C4-ST</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_head_frozen_resnet18</t>
+          <t>kaggle_fruits_quality_all_head_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3457,79 +3507,79 @@
           <t>state</t>
         </is>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>95.2</v>
+      <c r="D26" s="4" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>78.8</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>95.2</v>
+        <v>7.3</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>79.2</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>95.2</v>
+        <v>6.9</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>86.59999999999999</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>79.3</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>95.2</v>
+        <v>7.3</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>78.7</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0.904</v>
+        <v>7.4</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>0.727</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>0.58</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>0.9901</v>
+        <v>0.147</v>
+      </c>
+      <c r="S26" s="4" t="n">
+        <v>0.8827</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0.8671</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>0.123</v>
+        <v>0.0156</v>
       </c>
       <c r="V26" s="5" t="n">
-        <v>405.4</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>93.5</v>
+        <v>352.2</v>
+      </c>
+      <c r="W26" s="4" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="X26" s="5" t="n">
-        <v>85.40000000000001</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" ht="300" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>OWN-EB0-C4-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_head_layer4_efficientnet_b0</t>
+          <t>mendeley_fruits_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3538,78 +3588,78 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>95.8</v>
+        <v>95.2</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>78.8</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>17</v>
+        <v>16.4</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>95.8</v>
+        <v>95.2</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>79.2</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>16.6</v>
+        <v>16</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>95.8</v>
+        <v>95.2</v>
       </c>
       <c r="K27" s="5" t="n">
         <v>79.3</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>16.5</v>
+        <v>15.9</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>95.8</v>
+        <v>95.2</v>
       </c>
       <c r="N27" s="5" t="n">
         <v>78.7</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>17.1</v>
+        <v>16.5</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.917</v>
+        <v>0.904</v>
       </c>
       <c r="Q27" s="5" t="n">
         <v>0.58</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>0.337</v>
+        <v>0.324</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>0.9855</v>
+        <v>0.9901</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0.8671</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>0.1184</v>
+        <v>0.123</v>
       </c>
       <c r="V27" s="5" t="n">
-        <v>413.3</v>
-      </c>
-      <c r="W27" s="4" t="n">
-        <v>86.59999999999999</v>
+        <v>276.83</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>93.5</v>
       </c>
       <c r="X27" s="5" t="n">
-        <v>75.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="28" ht="300" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C4-ST</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_frozen_resnet18</t>
+          <t>mendeley_fruits_all_head_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3618,78 +3668,78 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>94.3</v>
+        <v>95.8</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>78.2</v>
+        <v>78.8</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>16.1</v>
+        <v>17</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>94.3</v>
+        <v>95.8</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>79.2</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>15.1</v>
+        <v>16.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <v>81.2</v>
+        <v>95.8</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>79.3</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>13.3</v>
+        <v>16.5</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>94.3</v>
+        <v>95.8</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>78</v>
+        <v>78.7</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="P28" s="4" t="n">
-        <v>0.888</v>
+        <v>17.1</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>0.917</v>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>0.591</v>
+        <v>0.58</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>0.297</v>
+        <v>0.337</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0.9816</v>
+        <v>0.9855</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>0.8951</v>
+        <v>0.8671</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.1184</v>
       </c>
       <c r="V28" s="5" t="n">
-        <v>330.85</v>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>294.63</v>
+      </c>
+      <c r="W28" s="4" t="n">
+        <v>86.59999999999999</v>
       </c>
       <c r="X28" s="5" t="n">
-        <v>75.5</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="29" ht="300" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>OWN-EB0-C1-ST</t>
+          <t>OWN-R18-C1-ST</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_frozen_efficientnet_b0</t>
+          <t>mendeley_fruits_all_frozen_resnet18</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3698,78 +3748,78 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>96.7</v>
+        <v>94.3</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>78.2</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>18.5</v>
+        <v>16.1</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>96.7</v>
+        <v>94.3</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>79.2</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>17.5</v>
+        <v>15.1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>96.7</v>
+        <v>94.5</v>
       </c>
       <c r="K29" s="4" t="n">
         <v>81.2</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>15.5</v>
+        <v>13.3</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>96.7</v>
+        <v>94.3</v>
       </c>
       <c r="N29" s="5" t="n">
         <v>78</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>0.9340000000000001</v>
+        <v>16.3</v>
+      </c>
+      <c r="P29" s="4" t="n">
+        <v>0.888</v>
       </c>
       <c r="Q29" s="5" t="n">
         <v>0.591</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>0.343</v>
+        <v>0.297</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>0.9959</v>
-      </c>
-      <c r="T29" s="3" t="n">
-        <v>0.972</v>
+        <v>0.9816</v>
+      </c>
+      <c r="T29" s="4" t="n">
+        <v>0.8951</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>0.0239</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="V29" s="5" t="n">
-        <v>370.88</v>
+        <v>417.26</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>97.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="X29" s="5" t="n">
-        <v>76.09999999999999</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="30" ht="300" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>OWN-R18-C2-ST</t>
+          <t>OWN-EB0-C1-ST</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_layer4_resnet18</t>
+          <t>mendeley_lemon_varieties_all_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3778,78 +3828,78 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>99.8</v>
+        <v>96.7</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>75</v>
+        <v>78.2</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>24.8</v>
+        <v>18.5</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>99.8</v>
+        <v>96.7</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>75</v>
+        <v>79.2</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>24.8</v>
+        <v>17.5</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>75.5</v>
+        <v>96.7</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>81.2</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>24.3</v>
+        <v>15.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>99.8</v>
+        <v>96.7</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>75.5</v>
+        <v>78</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>24.3</v>
+        <v>18.7</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0.996</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>0.51</v>
+        <v>0.591</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>0.486</v>
+        <v>0.343</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T30" s="4" t="n">
-        <v>0.8252</v>
+        <v>0.9959</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>0.972</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>0.1748</v>
+        <v>0.0239</v>
       </c>
       <c r="V30" s="5" t="n">
-        <v>339.63</v>
+        <v>387.76</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>96.7</v>
+        <v>97.5</v>
       </c>
       <c r="X30" s="5" t="n">
-        <v>90.2</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="31" ht="300" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-R18-C2-ST</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_fresh_rotten_all_layer4_resnet18</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3858,78 +3908,78 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>74.3</v>
+        <v>75</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>20.3</v>
+        <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>75</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>19.6</v>
+        <v>24.8</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>82.3</v>
+        <v>99.8</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>75.5</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>12.4</v>
+        <v>24.3</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>94.7</v>
+        <v>99.8</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>76.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="P31" s="4" t="n">
-        <v>0.894</v>
+        <v>24.3</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>0.996</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="R31" s="2" t="n">
-        <v>0.304</v>
+        <v>0.486</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0.9912</v>
+        <v>1</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.8881</v>
+        <v>0.8252</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>0.1031</v>
+        <v>0.1748</v>
       </c>
       <c r="V31" s="5" t="n">
-        <v>395.42</v>
-      </c>
-      <c r="W31" s="4" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="X31" s="4" t="n">
-        <v>70.09999999999999</v>
+        <v>274.91</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="X31" s="5" t="n">
+        <v>90.2</v>
       </c>
     </row>
     <row r="32" ht="300" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>OWN-R18-C4-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_head_layer4_resnet18</t>
+          <t>mendeley_lemon_varieties_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3938,78 +3988,78 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>99.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>70.8</v>
+        <v>74.3</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>29</v>
+        <v>20.3</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>99.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>70.8</v>
+        <v>75</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>29</v>
+        <v>19.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>70.8</v>
+        <v>94.7</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>82.3</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>29</v>
+        <v>12.4</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>99.8</v>
+        <v>94.7</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>71</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>0.996</v>
+        <v>17.8</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>0.894</v>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>0.418</v>
+        <v>0.59</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>0.578</v>
+        <v>0.304</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T32" s="5" t="n">
-        <v>0.7902</v>
+        <v>0.9912</v>
+      </c>
+      <c r="T32" s="4" t="n">
+        <v>0.8881</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>0.2098</v>
+        <v>0.1031</v>
       </c>
       <c r="V32" s="5" t="n">
-        <v>463.91</v>
-      </c>
-      <c r="W32" s="3" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="X32" s="5" t="n">
-        <v>83.8</v>
+        <v>350.65</v>
+      </c>
+      <c r="W32" s="4" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="X32" s="4" t="n">
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="33" ht="300" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-R18-C4-ST</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_head_frozen_resnet18</t>
+          <t>kaggle_fruits_fresh_rotten_all_head_layer4_resnet18</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -4018,78 +4068,78 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>96.2</v>
+        <v>99.8</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>70.8</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>25.4</v>
+        <v>29</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>96.2</v>
+        <v>99.8</v>
       </c>
       <c r="H33" s="5" t="n">
         <v>70.8</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>25.4</v>
+        <v>29</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>96.3</v>
+        <v>99.8</v>
       </c>
       <c r="K33" s="5" t="n">
         <v>70.8</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>25.5</v>
+        <v>29</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>96.2</v>
+        <v>99.8</v>
       </c>
       <c r="N33" s="5" t="n">
         <v>71</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>25.2</v>
+        <v>28.8</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0.925</v>
+        <v>0.996</v>
       </c>
       <c r="Q33" s="5" t="n">
         <v>0.418</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>0.507</v>
+        <v>0.578</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>0.9958</v>
-      </c>
-      <c r="T33" s="4" t="n">
-        <v>0.8391999999999999</v>
+        <v>1</v>
+      </c>
+      <c r="T33" s="5" t="n">
+        <v>0.7902</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>0.1566</v>
+        <v>0.2098</v>
       </c>
       <c r="V33" s="5" t="n">
-        <v>340.66</v>
-      </c>
-      <c r="W33" s="4" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="X33" s="4" t="n">
-        <v>72.09999999999999</v>
+        <v>313.74</v>
+      </c>
+      <c r="W33" s="3" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="X33" s="5" t="n">
+        <v>83.8</v>
       </c>
     </row>
     <row r="34" ht="300" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>OWN-EB0-C4-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_head_layer4_efficientnet_b0</t>
+          <t>mendeley_lemon_varieties_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -4098,78 +4148,78 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>99.7</v>
+        <v>96.2</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>65.7</v>
+        <v>70.8</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>34</v>
+        <v>25.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>99.7</v>
+        <v>96.2</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>66.7</v>
+        <v>70.8</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>33</v>
+        <v>25.4</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>66.7</v>
+        <v>70.8</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>32.9</v>
+        <v>25.5</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>99.7</v>
+        <v>96.2</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>65.7</v>
+        <v>71</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>34</v>
+        <v>25.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0.993</v>
+        <v>0.925</v>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>0.324</v>
+        <v>0.418</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>0.669</v>
+        <v>0.507</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T34" s="5" t="n">
-        <v>0.7343</v>
+        <v>0.9958</v>
+      </c>
+      <c r="T34" s="4" t="n">
+        <v>0.8391999999999999</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>0.2657</v>
+        <v>0.1566</v>
       </c>
       <c r="V34" s="5" t="n">
-        <v>540.1900000000001</v>
-      </c>
-      <c r="W34" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="X34" s="5" t="n">
-        <v>84.59999999999999</v>
+        <v>354.54</v>
+      </c>
+      <c r="W34" s="4" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="X34" s="4" t="n">
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="35" ht="300" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-EB0-C4-ST</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_fresh_rotten_all_head_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -4178,78 +4228,78 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>65.7</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>32.9</v>
+        <v>34</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="H35" s="5" t="n">
         <v>66.7</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>31.9</v>
+        <v>33</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>98.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="K35" s="5" t="n">
         <v>66.7</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>31.8</v>
+        <v>32.9</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>98.8</v>
+        <v>99.7</v>
       </c>
       <c r="N35" s="5" t="n">
         <v>65.7</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>33.1</v>
+        <v>34</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0.973</v>
+        <v>0.993</v>
       </c>
       <c r="Q35" s="5" t="n">
         <v>0.324</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>0.649</v>
+        <v>0.669</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>0.9994</v>
+        <v>1</v>
       </c>
       <c r="T35" s="5" t="n">
-        <v>0.7762</v>
+        <v>0.7343</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>0.2232</v>
+        <v>0.2657</v>
       </c>
       <c r="V35" s="5" t="n">
-        <v>357.03</v>
+        <v>413.66</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="X35" s="5" t="n">
-        <v>82.7</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="36" ht="300" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_frozen_resnet18</t>
+          <t>kaggle_fruits_fresh_rotten_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -4258,67 +4308,67 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>96.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>59.7</v>
+        <v>65.7</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>36.5</v>
+        <v>32.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>96.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>66.7</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>29.5</v>
+        <v>31.9</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="K36" s="4" t="n">
-        <v>81</v>
+        <v>98.5</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>66.7</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>15.3</v>
+        <v>31.8</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>96.2</v>
+        <v>98.8</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>63.6</v>
+        <v>65.7</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>32.6</v>
+        <v>33.1</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.925</v>
+        <v>0.973</v>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>0.411</v>
+        <v>0.324</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>0.514</v>
+        <v>0.649</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.9916</v>
-      </c>
-      <c r="T36" s="4" t="n">
-        <v>0.8671</v>
+        <v>0.9994</v>
+      </c>
+      <c r="T36" s="5" t="n">
+        <v>0.7762</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>0.1245</v>
+        <v>0.2232</v>
       </c>
       <c r="V36" s="5" t="n">
-        <v>309.16</v>
-      </c>
-      <c r="W36" s="4" t="n">
-        <v>89.7</v>
+        <v>260.97</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>90.90000000000001</v>
       </c>
       <c r="X36" s="5" t="n">
-        <v>78.90000000000001</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="37" ht="300" customHeight="1">
@@ -4329,75 +4379,235 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
+          <t>mendeley_lemon_varieties_all_frozen_resnet18</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="Q37" s="5" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>0.9916</v>
+      </c>
+      <c r="T37" s="4" t="n">
+        <v>0.8671</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>0.1245</v>
+      </c>
+      <c r="V37" s="5" t="n">
+        <v>323.94</v>
+      </c>
+      <c r="W37" s="4" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="X37" s="5" t="n">
+        <v>78.90000000000001</v>
+      </c>
+    </row>
+    <row r="38" ht="300" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>OWN-EB2-C1-ST</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>kaggle_fruits_fresh_rotten_all_frozen_efficientnet_b2</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="Q38" s="5" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="T38" s="5" t="n">
+        <v>0.6573</v>
+      </c>
+      <c r="U38" s="2" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="V38" s="5" t="n">
+        <v>343.62</v>
+      </c>
+      <c r="W38" s="5" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="X38" s="4" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" ht="300" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>OWN-R18-C1-ST</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>kaggle_fruits_quality_all_frozen_resnet18</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="n">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E39" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="F39" s="2" t="n">
         <v>28.1</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H39" s="5" t="n">
         <v>58.3</v>
       </c>
-      <c r="I37" s="2" t="n">
+      <c r="I39" s="2" t="n">
         <v>27.8</v>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="J39" s="4" t="n">
         <v>86.2</v>
       </c>
-      <c r="K37" s="5" t="n">
+      <c r="K39" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="L37" s="2" t="n">
+      <c r="L39" s="2" t="n">
         <v>26.2</v>
       </c>
-      <c r="M37" s="4" t="n">
+      <c r="M39" s="4" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="N37" s="5" t="n">
+      <c r="N39" s="5" t="n">
         <v>59.4</v>
       </c>
-      <c r="O37" s="2" t="n">
+      <c r="O39" s="2" t="n">
         <v>26.7</v>
       </c>
-      <c r="P37" s="5" t="n">
+      <c r="P39" s="5" t="n">
         <v>0.732</v>
       </c>
-      <c r="Q37" s="5" t="n">
+      <c r="Q39" s="5" t="n">
         <v>0.194</v>
       </c>
-      <c r="R37" s="2" t="n">
+      <c r="R39" s="2" t="n">
         <v>0.538</v>
       </c>
-      <c r="S37" s="3" t="n">
+      <c r="S39" s="3" t="n">
         <v>0.9136</v>
       </c>
-      <c r="T37" s="4" t="n">
+      <c r="T39" s="4" t="n">
         <v>0.8531</v>
       </c>
-      <c r="U37" s="2" t="n">
+      <c r="U39" s="2" t="n">
         <v>0.0605</v>
       </c>
-      <c r="V37" s="5" t="n">
-        <v>352.47</v>
-      </c>
-      <c r="W37" s="5" t="n">
+      <c r="V39" s="5" t="n">
+        <v>348.08</v>
+      </c>
+      <c r="W39" s="5" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="X37" s="3" t="n">
+      <c r="X39" s="3" t="n">
         <v>57.6</v>
       </c>
     </row>
@@ -4413,7 +4623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4565,7 +4775,7 @@
         <v>0.993</v>
       </c>
       <c r="N2" s="9" t="n">
-        <v>623.8200000000001</v>
+        <v>332.17</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>87.09999999999999</v>
@@ -4623,7 +4833,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>469.04</v>
+        <v>331.42</v>
       </c>
       <c r="O3" s="7" t="n">
         <v>91.8</v>
@@ -4681,7 +4891,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>335.3</v>
+        <v>371.77</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>88.5</v>
@@ -4739,7 +4949,7 @@
         <v>0.8741</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>362.15</v>
+        <v>256.86</v>
       </c>
       <c r="O5" s="7" t="n">
         <v>96.59999999999999</v>
@@ -4797,7 +5007,7 @@
         <v>0.8951</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>519.98</v>
+        <v>409.89</v>
       </c>
       <c r="O6" s="7" t="n">
         <v>92</v>
@@ -4855,7 +5065,7 @@
         <v>0.9301</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>329.88</v>
+        <v>348.16</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>89.7</v>
@@ -4913,7 +5123,7 @@
         <v>0.9161</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>285.52</v>
+        <v>439.11</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>86.3</v>
@@ -4971,7 +5181,7 @@
         <v>0.9441000000000001</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>291.59</v>
+        <v>444.53</v>
       </c>
       <c r="O9" s="7" t="n">
         <v>93.90000000000001</v>
@@ -5029,7 +5239,7 @@
         <v>0.9091</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>385.14</v>
+        <v>273.67</v>
       </c>
       <c r="O10" s="7" t="n">
         <v>97.3</v>
@@ -5087,7 +5297,7 @@
         <v>0.951</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>402.49</v>
+        <v>425.73</v>
       </c>
       <c r="O11" s="7" t="n">
         <v>95.3</v>
@@ -5145,7 +5355,7 @@
         <v>0.9441000000000001</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>399.7</v>
+        <v>428.54</v>
       </c>
       <c r="O12" s="7" t="n">
         <v>94.90000000000001</v>
@@ -5203,7 +5413,7 @@
         <v>0.9301</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>361.02</v>
+        <v>361.53</v>
       </c>
       <c r="O13" s="7" t="n">
         <v>93.09999999999999</v>
@@ -5218,12 +5428,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C1-ST</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fresh_stale_all_frozen_resnet18</t>
+          <t>kaggle_fresh_stale_all_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -5237,13 +5447,13 @@
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>83.2</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>11.8</v>
+        <v>13.8</v>
       </c>
       <c r="I14" s="8" t="n">
         <v>83.3</v>
@@ -5257,17 +5467,17 @@
       <c r="L14" s="9" t="n">
         <v>0.664</v>
       </c>
-      <c r="M14" s="8" t="n">
-        <v>0.8881</v>
+      <c r="M14" s="7" t="n">
+        <v>0.9441000000000001</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>474.84</v>
+        <v>502.89</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="P14" s="9" t="n">
-        <v>87.90000000000001</v>
+        <v>91.7</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -5276,12 +5486,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-R18-C1-ST</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fresh_stale_all_head_frozen_resnet18</t>
+          <t>kaggle_fresh_stale_all_frozen_resnet18</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -5295,13 +5505,13 @@
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>83.2</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>14.8</v>
+        <v>11.8</v>
       </c>
       <c r="I15" s="8" t="n">
         <v>83.3</v>
@@ -5316,16 +5526,16 @@
         <v>0.664</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.8951</v>
+        <v>0.8881</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>368.93</v>
+        <v>476.71</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>95.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>76.8</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -5334,12 +5544,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C4-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_head_layer4_resnet18</t>
+          <t>kaggle_fresh_stale_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -5352,14 +5562,14 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F16" s="8" t="n">
-        <v>88.90000000000001</v>
+      <c r="F16" s="7" t="n">
+        <v>98</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>83.2</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>5.7</v>
+        <v>14.8</v>
       </c>
       <c r="I16" s="8" t="n">
         <v>83.3</v>
@@ -5374,16 +5584,16 @@
         <v>0.664</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.8741</v>
+        <v>0.8951</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>429.45</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>87.7</v>
+        <v>260.52</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>95.7</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>88.09999999999999</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -5392,12 +5602,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C1-ST</t>
+          <t>OWN-R18-C4-ST</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_frozen_efficientnet_b0</t>
+          <t>kaggle_fruits_quality_all_head_layer4_resnet18</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -5411,37 +5621,37 @@
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>84.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>1.8</v>
+        <v>83.2</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>5.7</v>
       </c>
       <c r="I17" s="8" t="n">
         <v>83.3</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>84.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>82.5</v>
+        <v>83.2</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.669</v>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>0.951</v>
+        <v>0.664</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>0.8741</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>328.35</v>
+        <v>344.09</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>89.59999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>79</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -5450,12 +5660,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-EB0-C1-ST</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_head_frozen_resnet18</t>
+          <t>kaggle_fruits_quality_all_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -5469,13 +5679,13 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>86</v>
+        <v>84.7</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="I18" s="8" t="n">
         <v>83.3</v>
@@ -5489,17 +5699,17 @@
       <c r="L18" s="9" t="n">
         <v>0.669</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>0.8322000000000001</v>
+      <c r="M18" s="7" t="n">
+        <v>0.951</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>335.32</v>
+        <v>370.7</v>
       </c>
       <c r="O18" s="8" t="n">
-        <v>89.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>89.09999999999999</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -5508,12 +5718,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_quality_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -5526,14 +5736,14 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F19" s="7" t="n">
-        <v>91.5</v>
+      <c r="F19" s="8" t="n">
+        <v>86</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="H19" s="8" t="n">
-        <v>8.6</v>
+      <c r="H19" s="7" t="n">
+        <v>3.1</v>
       </c>
       <c r="I19" s="8" t="n">
         <v>83.3</v>
@@ -5548,16 +5758,16 @@
         <v>0.669</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.8881</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>380.33</v>
+        <v>357.29</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P19" s="9" t="n">
-        <v>84.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -5566,12 +5776,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C3-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_head_frozen_efficientnet_b0</t>
+          <t>mendeley_fruits_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -5585,13 +5795,13 @@
         </is>
       </c>
       <c r="F20" s="7" t="n">
-        <v>98.7</v>
+        <v>91.5</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="H20" s="9" t="n">
-        <v>15.8</v>
+      <c r="H20" s="8" t="n">
+        <v>8.6</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>83.3</v>
@@ -5605,17 +5815,17 @@
       <c r="L20" s="9" t="n">
         <v>0.669</v>
       </c>
-      <c r="M20" s="7" t="n">
-        <v>0.958</v>
+      <c r="M20" s="8" t="n">
+        <v>0.8881</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>324.19</v>
-      </c>
-      <c r="O20" s="7" t="n">
-        <v>98.2</v>
+        <v>407.64</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>88.59999999999999</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>91.5</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -5624,12 +5834,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C3-ST</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_frozen_resnet18</t>
+          <t>mendeley_lemon_varieties_all_head_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -5643,37 +5853,37 @@
         </is>
       </c>
       <c r="F21" s="7" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>79.09999999999999</v>
+        <v>98.7</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>82.90000000000001</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="K21" s="9" t="n">
-        <v>79.40000000000001</v>
+        <v>15.8</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>82.5</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="M21" s="8" t="n">
-        <v>0.8462</v>
+        <v>0.669</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>0.958</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>350.7</v>
+        <v>330.89</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>96.2</v>
+        <v>98.2</v>
       </c>
       <c r="P21" s="9" t="n">
-        <v>85</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -5682,12 +5892,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-R18-C1-ST</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_fresh_rotten_all_frozen_resnet18</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -5700,14 +5910,14 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F22" s="8" t="n">
-        <v>86.09999999999999</v>
+      <c r="F22" s="7" t="n">
+        <v>97.59999999999999</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="H22" s="8" t="n">
-        <v>7</v>
+      <c r="H22" s="9" t="n">
+        <v>18.5</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>79.2</v>
@@ -5721,17 +5931,17 @@
       <c r="L22" s="9" t="n">
         <v>0.585</v>
       </c>
-      <c r="M22" s="7" t="n">
-        <v>0.9091</v>
+      <c r="M22" s="8" t="n">
+        <v>0.8462</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>332.3</v>
-      </c>
-      <c r="O22" s="8" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>73.8</v>
+        <v>343.39</v>
+      </c>
+      <c r="O22" s="7" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="P22" s="9" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -5740,12 +5950,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C2-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fresh_stale_all_layer4_resnet18</t>
+          <t>kaggle_fruits_quality_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -5758,38 +5968,38 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F23" s="7" t="n">
-        <v>98.90000000000001</v>
+      <c r="F23" s="8" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>20.1</v>
+        <v>79.09999999999999</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="I23" s="9" t="n">
         <v>79.2</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>78.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="M23" s="8" t="n">
-        <v>0.8811</v>
+        <v>0.585</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>0.9091</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>396.21</v>
-      </c>
-      <c r="O23" s="7" t="n">
-        <v>96</v>
-      </c>
-      <c r="P23" s="9" t="n">
-        <v>81.2</v>
+        <v>367.21</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="P23" s="8" t="n">
+        <v>73.8</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -5798,12 +6008,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-R18-C2-ST</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_head_frozen_resnet18</t>
+          <t>kaggle_fresh_stale_all_layer4_resnet18</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -5817,13 +6027,13 @@
         </is>
       </c>
       <c r="F24" s="7" t="n">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>78.8</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>20.6</v>
+        <v>20.1</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>79.2</v>
@@ -5838,16 +6048,16 @@
         <v>0.58</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8811</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>519.6</v>
+        <v>308.36</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>97.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="P24" s="9" t="n">
-        <v>89.40000000000001</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -5856,12 +6066,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C4-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_head_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_fresh_rotten_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -5874,14 +6084,14 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F25" s="8" t="n">
-        <v>86.09999999999999</v>
+      <c r="F25" s="7" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>78.8</v>
       </c>
-      <c r="H25" s="8" t="n">
-        <v>7.3</v>
+      <c r="H25" s="9" t="n">
+        <v>20.6</v>
       </c>
       <c r="I25" s="9" t="n">
         <v>79.2</v>
@@ -5896,16 +6106,16 @@
         <v>0.58</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.8671</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>382.52</v>
-      </c>
-      <c r="O25" s="8" t="n">
+        <v>421.72</v>
+      </c>
+      <c r="O25" s="7" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="P25" s="9" t="n">
         <v>89.40000000000001</v>
-      </c>
-      <c r="P25" s="9" t="n">
-        <v>84</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5914,12 +6124,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-EB0-C4-ST</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_head_frozen_resnet18</t>
+          <t>kaggle_fruits_quality_all_head_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -5932,14 +6142,14 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F26" s="7" t="n">
-        <v>95.2</v>
+      <c r="F26" s="8" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>78.8</v>
       </c>
-      <c r="H26" s="9" t="n">
-        <v>16.4</v>
+      <c r="H26" s="8" t="n">
+        <v>7.3</v>
       </c>
       <c r="I26" s="9" t="n">
         <v>79.2</v>
@@ -5957,13 +6167,13 @@
         <v>0.8671</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>405.4</v>
-      </c>
-      <c r="O26" s="7" t="n">
-        <v>93.5</v>
+        <v>352.2</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="P26" s="9" t="n">
-        <v>85.40000000000001</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -5972,12 +6182,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C4-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_head_layer4_efficientnet_b0</t>
+          <t>mendeley_fruits_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -5991,13 +6201,13 @@
         </is>
       </c>
       <c r="F27" s="7" t="n">
-        <v>95.8</v>
+        <v>95.2</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>78.8</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>17</v>
+        <v>16.4</v>
       </c>
       <c r="I27" s="9" t="n">
         <v>79.2</v>
@@ -6015,13 +6225,13 @@
         <v>0.8671</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>413.3</v>
-      </c>
-      <c r="O27" s="8" t="n">
-        <v>86.59999999999999</v>
+        <v>276.83</v>
+      </c>
+      <c r="O27" s="7" t="n">
+        <v>93.5</v>
       </c>
       <c r="P27" s="9" t="n">
-        <v>75.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -6030,12 +6240,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C4-ST</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_frozen_resnet18</t>
+          <t>mendeley_fruits_all_head_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -6049,37 +6259,37 @@
         </is>
       </c>
       <c r="F28" s="7" t="n">
-        <v>94.3</v>
+        <v>95.8</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>78.2</v>
+        <v>78.8</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>16.1</v>
+        <v>17</v>
       </c>
       <c r="I28" s="9" t="n">
         <v>79.2</v>
       </c>
-      <c r="J28" s="8" t="n">
-        <v>81.2</v>
+      <c r="J28" s="9" t="n">
+        <v>79.3</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>78</v>
+        <v>78.7</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.591</v>
+        <v>0.58</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.8951</v>
+        <v>0.8671</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>330.85</v>
-      </c>
-      <c r="O28" s="7" t="n">
-        <v>92.90000000000001</v>
+        <v>294.63</v>
+      </c>
+      <c r="O28" s="8" t="n">
+        <v>86.59999999999999</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>75.5</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -6088,12 +6298,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C1-ST</t>
+          <t>OWN-R18-C1-ST</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_frozen_efficientnet_b0</t>
+          <t>mendeley_fruits_all_frozen_resnet18</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -6107,13 +6317,13 @@
         </is>
       </c>
       <c r="F29" s="7" t="n">
-        <v>96.7</v>
+        <v>94.3</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>78.2</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>18.5</v>
+        <v>16.1</v>
       </c>
       <c r="I29" s="9" t="n">
         <v>79.2</v>
@@ -6127,17 +6337,17 @@
       <c r="L29" s="9" t="n">
         <v>0.591</v>
       </c>
-      <c r="M29" s="7" t="n">
-        <v>0.972</v>
+      <c r="M29" s="8" t="n">
+        <v>0.8951</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>370.88</v>
+        <v>417.26</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>97.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P29" s="9" t="n">
-        <v>76.09999999999999</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -6146,12 +6356,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C2-ST</t>
+          <t>OWN-EB0-C1-ST</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_layer4_resnet18</t>
+          <t>mendeley_lemon_varieties_all_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -6165,37 +6375,37 @@
         </is>
       </c>
       <c r="F30" s="7" t="n">
-        <v>99.8</v>
+        <v>96.7</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>75</v>
+        <v>78.2</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>24.8</v>
+        <v>18.5</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>75</v>
-      </c>
-      <c r="J30" s="9" t="n">
-        <v>75.5</v>
+        <v>79.2</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>81.2</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>75.5</v>
+        <v>78</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="M30" s="8" t="n">
-        <v>0.8252</v>
+        <v>0.591</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>0.972</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>339.63</v>
+        <v>387.76</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>96.7</v>
+        <v>97.5</v>
       </c>
       <c r="P30" s="9" t="n">
-        <v>90.2</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -6204,12 +6414,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-R18-C2-ST</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_fresh_rotten_all_layer4_resnet18</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -6223,37 +6433,37 @@
         </is>
       </c>
       <c r="F31" s="7" t="n">
-        <v>94.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>74.3</v>
+        <v>75</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>20.3</v>
+        <v>24.8</v>
       </c>
       <c r="I31" s="9" t="n">
         <v>75</v>
       </c>
-      <c r="J31" s="8" t="n">
-        <v>82.3</v>
+      <c r="J31" s="9" t="n">
+        <v>75.5</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>76.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.8881</v>
+        <v>0.8252</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>395.42</v>
-      </c>
-      <c r="O31" s="8" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="P31" s="8" t="n">
-        <v>70.09999999999999</v>
+        <v>274.91</v>
+      </c>
+      <c r="O31" s="7" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="P31" s="9" t="n">
+        <v>90.2</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -6262,12 +6472,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C4-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_head_layer4_resnet18</t>
+          <t>mendeley_lemon_varieties_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -6281,37 +6491,37 @@
         </is>
       </c>
       <c r="F32" s="7" t="n">
-        <v>99.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>70.8</v>
+        <v>74.3</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>29</v>
+        <v>20.3</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>70.8</v>
+        <v>75</v>
+      </c>
+      <c r="J32" s="8" t="n">
+        <v>82.3</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>71</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="M32" s="9" t="n">
-        <v>0.7902</v>
+        <v>0.59</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>0.8881</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>463.91</v>
-      </c>
-      <c r="O32" s="7" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="P32" s="9" t="n">
-        <v>83.8</v>
+        <v>350.65</v>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="P32" s="8" t="n">
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -6320,12 +6530,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-R18-C4-ST</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_head_frozen_resnet18</t>
+          <t>kaggle_fruits_fresh_rotten_all_head_layer4_resnet18</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -6339,13 +6549,13 @@
         </is>
       </c>
       <c r="F33" s="7" t="n">
-        <v>96.2</v>
+        <v>99.8</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>70.8</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>25.4</v>
+        <v>29</v>
       </c>
       <c r="I33" s="9" t="n">
         <v>70.8</v>
@@ -6359,17 +6569,17 @@
       <c r="L33" s="9" t="n">
         <v>0.418</v>
       </c>
-      <c r="M33" s="8" t="n">
-        <v>0.8391999999999999</v>
+      <c r="M33" s="9" t="n">
+        <v>0.7902</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>340.66</v>
-      </c>
-      <c r="O33" s="8" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="P33" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>313.74</v>
+      </c>
+      <c r="O33" s="7" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="P33" s="9" t="n">
+        <v>83.8</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -6378,12 +6588,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C4-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_head_layer4_efficientnet_b0</t>
+          <t>mendeley_lemon_varieties_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -6397,37 +6607,37 @@
         </is>
       </c>
       <c r="F34" s="7" t="n">
-        <v>99.7</v>
+        <v>96.2</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>65.7</v>
+        <v>70.8</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>34</v>
+        <v>25.4</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>66.7</v>
+        <v>70.8</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>66.7</v>
+        <v>70.8</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>65.7</v>
+        <v>71</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="M34" s="9" t="n">
-        <v>0.7343</v>
+        <v>0.418</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>0.8391999999999999</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>540.1900000000001</v>
-      </c>
-      <c r="O34" s="7" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="P34" s="9" t="n">
-        <v>84.59999999999999</v>
+        <v>354.54</v>
+      </c>
+      <c r="O34" s="8" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="P34" s="8" t="n">
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -6436,12 +6646,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-EB0-C4-ST</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_fresh_rotten_all_head_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -6455,13 +6665,13 @@
         </is>
       </c>
       <c r="F35" s="7" t="n">
-        <v>98.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>65.7</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>32.9</v>
+        <v>34</v>
       </c>
       <c r="I35" s="9" t="n">
         <v>66.7</v>
@@ -6476,16 +6686,16 @@
         <v>0.324</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.7762</v>
+        <v>0.7343</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>357.03</v>
+        <v>413.66</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>90.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="P35" s="9" t="n">
-        <v>82.7</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6494,12 +6704,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_frozen_resnet18</t>
+          <t>kaggle_fruits_fresh_rotten_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -6513,37 +6723,37 @@
         </is>
       </c>
       <c r="F36" s="7" t="n">
-        <v>96.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>59.7</v>
+        <v>65.7</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>36.5</v>
+        <v>32.9</v>
       </c>
       <c r="I36" s="9" t="n">
         <v>66.7</v>
       </c>
-      <c r="J36" s="8" t="n">
-        <v>81</v>
+      <c r="J36" s="9" t="n">
+        <v>66.7</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>63.6</v>
+        <v>65.7</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>0.8671</v>
+        <v>0.324</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>0.7762</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>309.16</v>
-      </c>
-      <c r="O36" s="8" t="n">
-        <v>89.7</v>
+        <v>260.97</v>
+      </c>
+      <c r="O36" s="7" t="n">
+        <v>90.90000000000001</v>
       </c>
       <c r="P36" s="9" t="n">
-        <v>78.90000000000001</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -6557,50 +6767,166 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
+          <t>mendeley_lemon_varieties_all_frozen_resnet18</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>own_dataset</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="I37" s="9" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>0.8671</v>
+      </c>
+      <c r="N37" s="9" t="n">
+        <v>323.94</v>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="P37" s="9" t="n">
+        <v>78.90000000000001</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>OWN-EB2-C1-ST</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>kaggle_fruits_fresh_rotten_all_frozen_efficientnet_b2</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>own_dataset</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="I38" s="9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="L38" s="9" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="M38" s="9" t="n">
+        <v>0.6573</v>
+      </c>
+      <c r="N38" s="9" t="n">
+        <v>343.62</v>
+      </c>
+      <c r="O38" s="9" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="P38" s="8" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>OWN-R18-C1-ST</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
           <t>kaggle_fruits_quality_all_frozen_resnet18</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>own_dataset</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="n">
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>own_dataset</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="G37" s="9" t="n">
+      <c r="G39" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="H37" s="9" t="n">
+      <c r="H39" s="9" t="n">
         <v>28.1</v>
       </c>
-      <c r="I37" s="9" t="n">
+      <c r="I39" s="9" t="n">
         <v>58.3</v>
       </c>
-      <c r="J37" s="9" t="n">
+      <c r="J39" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K39" s="9" t="n">
         <v>59.4</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L39" s="9" t="n">
         <v>0.194</v>
       </c>
-      <c r="M37" s="8" t="n">
+      <c r="M39" s="8" t="n">
         <v>0.8531</v>
       </c>
-      <c r="N37" s="9" t="n">
-        <v>352.47</v>
-      </c>
-      <c r="O37" s="9" t="n">
+      <c r="N39" s="9" t="n">
+        <v>348.08</v>
+      </c>
+      <c r="O39" s="9" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="P37" s="7" t="n">
+      <c r="P39" s="7" t="n">
         <v>57.6</v>
       </c>
     </row>
@@ -6615,7 +6941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6767,7 +7093,7 @@
         <v>0.9301</v>
       </c>
       <c r="N2" s="9" t="n">
-        <v>329.88</v>
+        <v>348.16</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>89.7</v>
@@ -6825,7 +7151,7 @@
         <v>0.951</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>328.35</v>
+        <v>370.7</v>
       </c>
       <c r="O3" s="8" t="n">
         <v>89.59999999999999</v>
@@ -6883,7 +7209,7 @@
         <v>0.8322000000000001</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>335.32</v>
+        <v>357.29</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>89.09999999999999</v>
@@ -6941,7 +7267,7 @@
         <v>0.993</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>623.8200000000001</v>
+        <v>332.17</v>
       </c>
       <c r="O5" s="8" t="n">
         <v>87.09999999999999</v>
@@ -6999,7 +7325,7 @@
         <v>0.9161</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>285.52</v>
+        <v>439.11</v>
       </c>
       <c r="O6" s="8" t="n">
         <v>86.3</v>
@@ -7057,7 +7383,7 @@
         <v>0.8741</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>429.45</v>
+        <v>344.09</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>87.7</v>
@@ -7115,7 +7441,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>469.04</v>
+        <v>331.42</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>91.8</v>
@@ -7173,7 +7499,7 @@
         <v>0.9091</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>332.3</v>
+        <v>367.21</v>
       </c>
       <c r="O9" s="8" t="n">
         <v>89.09999999999999</v>
@@ -7231,7 +7557,7 @@
         <v>0.8671</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>382.52</v>
+        <v>352.2</v>
       </c>
       <c r="O10" s="8" t="n">
         <v>89.40000000000001</v>
@@ -7289,7 +7615,7 @@
         <v>0.9441000000000001</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>291.59</v>
+        <v>444.53</v>
       </c>
       <c r="O11" s="7" t="n">
         <v>93.90000000000001</v>
@@ -7347,7 +7673,7 @@
         <v>0.9441000000000001</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>399.7</v>
+        <v>428.54</v>
       </c>
       <c r="O12" s="7" t="n">
         <v>94.90000000000001</v>
@@ -7405,7 +7731,7 @@
         <v>0.8881</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>380.33</v>
+        <v>407.64</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>88.59999999999999</v>
@@ -7463,7 +7789,7 @@
         <v>0.951</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>402.49</v>
+        <v>425.73</v>
       </c>
       <c r="O14" s="7" t="n">
         <v>95.3</v>
@@ -7521,7 +7847,7 @@
         <v>0.9091</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>385.14</v>
+        <v>273.67</v>
       </c>
       <c r="O15" s="7" t="n">
         <v>97.3</v>
@@ -7579,7 +7905,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>335.3</v>
+        <v>371.77</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>88.5</v>
@@ -7637,7 +7963,7 @@
         <v>0.8741</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>362.15</v>
+        <v>256.86</v>
       </c>
       <c r="O17" s="7" t="n">
         <v>96.59999999999999</v>
@@ -7695,7 +8021,7 @@
         <v>0.8881</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>474.84</v>
+        <v>476.71</v>
       </c>
       <c r="O18" s="7" t="n">
         <v>93.90000000000001</v>
@@ -7753,7 +8079,7 @@
         <v>0.9301</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>361.02</v>
+        <v>361.53</v>
       </c>
       <c r="O19" s="7" t="n">
         <v>93.09999999999999</v>
@@ -7811,7 +8137,7 @@
         <v>0.8951</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>519.98</v>
+        <v>409.89</v>
       </c>
       <c r="O20" s="7" t="n">
         <v>92</v>
@@ -7826,12 +8152,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-EB0-C1-ST</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fresh_stale_all_head_frozen_resnet18</t>
+          <t>kaggle_fresh_stale_all_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -7845,13 +8171,13 @@
         </is>
       </c>
       <c r="F21" s="7" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G21" s="8" t="n">
         <v>83.2</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>14.8</v>
+        <v>13.8</v>
       </c>
       <c r="I21" s="8" t="n">
         <v>83.3</v>
@@ -7865,17 +8191,17 @@
       <c r="L21" s="9" t="n">
         <v>0.664</v>
       </c>
-      <c r="M21" s="8" t="n">
-        <v>0.8951</v>
+      <c r="M21" s="7" t="n">
+        <v>0.9441000000000001</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>368.93</v>
+        <v>502.89</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="P21" s="9" t="n">
-        <v>76.8</v>
+        <v>91.7</v>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -7884,12 +8210,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C3-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_head_frozen_efficientnet_b0</t>
+          <t>kaggle_fresh_stale_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -7903,37 +8229,37 @@
         </is>
       </c>
       <c r="F22" s="7" t="n">
-        <v>98.7</v>
+        <v>98</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>15.8</v>
+        <v>83.2</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>14.8</v>
       </c>
       <c r="I22" s="8" t="n">
         <v>83.3</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>84.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>82.5</v>
+        <v>83.2</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.669</v>
-      </c>
-      <c r="M22" s="7" t="n">
-        <v>0.958</v>
+        <v>0.664</v>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>0.8951</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>324.19</v>
+        <v>260.52</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>98.2</v>
+        <v>95.7</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>91.5</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -7942,12 +8268,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C3-ST</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_frozen_resnet18</t>
+          <t>mendeley_lemon_varieties_all_head_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -7961,37 +8287,37 @@
         </is>
       </c>
       <c r="F23" s="7" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>78.2</v>
+        <v>98.7</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>82.90000000000001</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <v>79.2</v>
+        <v>15.8</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>83.3</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>78</v>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="K23" s="8" t="n">
+        <v>82.5</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="M23" s="8" t="n">
-        <v>0.8951</v>
+        <v>0.669</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>0.958</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>330.85</v>
+        <v>330.89</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>92.90000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="P23" s="9" t="n">
-        <v>75.5</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -8000,12 +8326,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-R18-C1-ST</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_head_frozen_resnet18</t>
+          <t>mendeley_fruits_all_frozen_resnet18</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -8019,37 +8345,37 @@
         </is>
       </c>
       <c r="F24" s="7" t="n">
-        <v>95.2</v>
+        <v>94.3</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>78.8</v>
+        <v>78.2</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>16.4</v>
+        <v>16.1</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>79.2</v>
       </c>
-      <c r="J24" s="9" t="n">
-        <v>79.3</v>
+      <c r="J24" s="8" t="n">
+        <v>81.2</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>78.7</v>
+        <v>78</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.58</v>
+        <v>0.591</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.8671</v>
+        <v>0.8951</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>405.4</v>
+        <v>417.26</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>93.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P24" s="9" t="n">
-        <v>85.40000000000001</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -8058,12 +8384,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C4-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_head_layer4_efficientnet_b0</t>
+          <t>mendeley_fruits_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -8077,13 +8403,13 @@
         </is>
       </c>
       <c r="F25" s="7" t="n">
-        <v>95.8</v>
+        <v>95.2</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>78.8</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>17</v>
+        <v>16.4</v>
       </c>
       <c r="I25" s="9" t="n">
         <v>79.2</v>
@@ -8101,13 +8427,13 @@
         <v>0.8671</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>413.3</v>
-      </c>
-      <c r="O25" s="8" t="n">
-        <v>86.59999999999999</v>
+        <v>276.83</v>
+      </c>
+      <c r="O25" s="7" t="n">
+        <v>93.5</v>
       </c>
       <c r="P25" s="9" t="n">
-        <v>75.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -8116,12 +8442,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C4-ST</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_frozen_resnet18</t>
+          <t>mendeley_fruits_all_head_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -8135,37 +8461,37 @@
         </is>
       </c>
       <c r="F26" s="7" t="n">
-        <v>97.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>79.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="I26" s="9" t="n">
         <v>79.2</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>79.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.585</v>
+        <v>0.58</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>0.8462</v>
+        <v>0.8671</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>350.7</v>
-      </c>
-      <c r="O26" s="7" t="n">
-        <v>96.2</v>
+        <v>294.63</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>86.59999999999999</v>
       </c>
       <c r="P26" s="9" t="n">
-        <v>85</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -8174,12 +8500,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C1-ST</t>
+          <t>OWN-R18-C1-ST</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_frozen_efficientnet_b0</t>
+          <t>kaggle_fruits_fresh_rotten_all_frozen_resnet18</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -8193,10 +8519,10 @@
         </is>
       </c>
       <c r="F27" s="7" t="n">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>78.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H27" s="9" t="n">
         <v>18.5</v>
@@ -8204,26 +8530,26 @@
       <c r="I27" s="9" t="n">
         <v>79.2</v>
       </c>
-      <c r="J27" s="8" t="n">
-        <v>81.2</v>
+      <c r="J27" s="9" t="n">
+        <v>79.2</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>78</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="M27" s="7" t="n">
-        <v>0.972</v>
+        <v>0.585</v>
+      </c>
+      <c r="M27" s="8" t="n">
+        <v>0.8462</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>370.88</v>
+        <v>343.39</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>97.5</v>
+        <v>96.2</v>
       </c>
       <c r="P27" s="9" t="n">
-        <v>76.09999999999999</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -8232,12 +8558,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C2-ST</t>
+          <t>OWN-EB0-C1-ST</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fresh_stale_all_layer4_resnet18</t>
+          <t>mendeley_lemon_varieties_all_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -8251,37 +8577,37 @@
         </is>
       </c>
       <c r="F28" s="7" t="n">
-        <v>98.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>78.8</v>
+        <v>78.2</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>20.1</v>
+        <v>18.5</v>
       </c>
       <c r="I28" s="9" t="n">
         <v>79.2</v>
       </c>
-      <c r="J28" s="9" t="n">
-        <v>79.3</v>
+      <c r="J28" s="8" t="n">
+        <v>81.2</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>78.7</v>
+        <v>78</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>0.8811</v>
+        <v>0.591</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>0.972</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>396.21</v>
+        <v>387.76</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>81.2</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -8290,12 +8616,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-R18-C2-ST</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_layer4_efficientnet_b0</t>
+          <t>kaggle_fresh_stale_all_layer4_resnet18</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -8309,37 +8635,37 @@
         </is>
       </c>
       <c r="F29" s="7" t="n">
-        <v>94.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>74.3</v>
+        <v>78.8</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>75</v>
-      </c>
-      <c r="J29" s="8" t="n">
-        <v>82.3</v>
+        <v>79.2</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>79.3</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>76.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>0.8881</v>
+        <v>0.8811</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>395.42</v>
-      </c>
-      <c r="O29" s="8" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="P29" s="8" t="n">
-        <v>70.09999999999999</v>
+        <v>308.36</v>
+      </c>
+      <c r="O29" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="P29" s="9" t="n">
+        <v>81.2</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -8348,12 +8674,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_head_frozen_resnet18</t>
+          <t>mendeley_lemon_varieties_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -8367,37 +8693,37 @@
         </is>
       </c>
       <c r="F30" s="7" t="n">
-        <v>99.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>78.8</v>
+        <v>74.3</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="J30" s="9" t="n">
-        <v>79.3</v>
+        <v>75</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>82.3</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>78.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8881</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>519.6</v>
-      </c>
-      <c r="O30" s="7" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="P30" s="9" t="n">
-        <v>89.40000000000001</v>
+        <v>350.65</v>
+      </c>
+      <c r="O30" s="8" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="P30" s="8" t="n">
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -8406,12 +8732,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C2-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_layer4_resnet18</t>
+          <t>kaggle_fruits_fresh_rotten_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -8425,37 +8751,37 @@
         </is>
       </c>
       <c r="F31" s="7" t="n">
-        <v>99.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>75</v>
+        <v>78.8</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>24.8</v>
+        <v>20.6</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>75</v>
+        <v>79.2</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>75.5</v>
+        <v>79.3</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>75.5</v>
+        <v>78.7</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.51</v>
+        <v>0.58</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.8252</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>339.63</v>
+        <v>421.72</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>96.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="P31" s="9" t="n">
-        <v>90.2</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -8464,12 +8790,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-R18-C2-ST</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_head_frozen_resnet18</t>
+          <t>kaggle_fruits_fresh_rotten_all_layer4_resnet18</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -8483,37 +8809,37 @@
         </is>
       </c>
       <c r="F32" s="7" t="n">
-        <v>96.2</v>
+        <v>99.8</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>70.8</v>
+        <v>75</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>25.4</v>
+        <v>24.8</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>70.8</v>
+        <v>75</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>70.8</v>
+        <v>75.5</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>71</v>
+        <v>75.5</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.418</v>
+        <v>0.51</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.8252</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>340.66</v>
-      </c>
-      <c r="O32" s="8" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="P32" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>274.91</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="P32" s="9" t="n">
+        <v>90.2</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -8522,12 +8848,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_frozen_resnet18</t>
+          <t>mendeley_lemon_varieties_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -8540,38 +8866,38 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F33" s="8" t="n">
-        <v>86.09999999999999</v>
+      <c r="F33" s="7" t="n">
+        <v>96.2</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>58</v>
+        <v>70.8</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>28.1</v>
+        <v>25.4</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>58.3</v>
+        <v>70.8</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>60</v>
+        <v>70.8</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>59.4</v>
+        <v>71</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.194</v>
+        <v>0.418</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.8531</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>352.47</v>
-      </c>
-      <c r="O33" s="9" t="n">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="P33" s="7" t="n">
-        <v>57.6</v>
+        <v>354.54</v>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="P33" s="8" t="n">
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -8580,12 +8906,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C4-ST</t>
+          <t>OWN-R18-C1-ST</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_head_layer4_resnet18</t>
+          <t>kaggle_fruits_quality_all_frozen_resnet18</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -8598,38 +8924,38 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F34" s="7" t="n">
-        <v>99.8</v>
+      <c r="F34" s="8" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>70.8</v>
+        <v>58</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>29</v>
+        <v>28.1</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>70.8</v>
+        <v>58.3</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>70.8</v>
+        <v>60</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>71</v>
+        <v>59.4</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="M34" s="9" t="n">
-        <v>0.7902</v>
+        <v>0.194</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>0.8531</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>463.91</v>
-      </c>
-      <c r="O34" s="7" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="P34" s="9" t="n">
-        <v>83.8</v>
+        <v>348.08</v>
+      </c>
+      <c r="O34" s="9" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="P34" s="7" t="n">
+        <v>57.6</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -8638,12 +8964,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-R18-C4-ST</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_fresh_rotten_all_head_layer4_resnet18</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -8657,37 +8983,37 @@
         </is>
       </c>
       <c r="F35" s="7" t="n">
-        <v>98.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>65.7</v>
+        <v>70.8</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>32.9</v>
+        <v>29</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>66.7</v>
+        <v>70.8</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>66.7</v>
+        <v>70.8</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>65.7</v>
+        <v>71</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.324</v>
+        <v>0.418</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.7762</v>
+        <v>0.7902</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>357.03</v>
+        <v>313.74</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>90.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="P35" s="9" t="n">
-        <v>82.7</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -8696,12 +9022,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C4-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_head_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_fresh_rotten_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -8715,13 +9041,13 @@
         </is>
       </c>
       <c r="F36" s="7" t="n">
-        <v>99.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>65.7</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>34</v>
+        <v>32.9</v>
       </c>
       <c r="I36" s="9" t="n">
         <v>66.7</v>
@@ -8736,16 +9062,16 @@
         <v>0.324</v>
       </c>
       <c r="M36" s="9" t="n">
-        <v>0.7343</v>
+        <v>0.7762</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>540.1900000000001</v>
+        <v>260.97</v>
       </c>
       <c r="O36" s="7" t="n">
-        <v>91.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P36" s="9" t="n">
-        <v>84.59999999999999</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -8754,12 +9080,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C4-ST</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_frozen_resnet18</t>
+          <t>kaggle_fruits_fresh_rotten_all_head_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -8773,37 +9099,153 @@
         </is>
       </c>
       <c r="F37" s="7" t="n">
-        <v>96.2</v>
+        <v>99.7</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>59.7</v>
+        <v>65.7</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>36.5</v>
+        <v>34</v>
       </c>
       <c r="I37" s="9" t="n">
         <v>66.7</v>
       </c>
-      <c r="J37" s="8" t="n">
+      <c r="J37" s="9" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>0.7343</v>
+      </c>
+      <c r="N37" s="9" t="n">
+        <v>413.66</v>
+      </c>
+      <c r="O37" s="7" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="P37" s="9" t="n">
+        <v>84.59999999999999</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>OWN-R18-C1-ST</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>mendeley_lemon_varieties_all_frozen_resnet18</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>own_dataset</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="I38" s="9" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J38" s="8" t="n">
         <v>81</v>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K38" s="9" t="n">
         <v>63.6</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L38" s="9" t="n">
         <v>0.411</v>
       </c>
-      <c r="M37" s="8" t="n">
+      <c r="M38" s="8" t="n">
         <v>0.8671</v>
       </c>
-      <c r="N37" s="9" t="n">
-        <v>309.16</v>
-      </c>
-      <c r="O37" s="8" t="n">
+      <c r="N38" s="9" t="n">
+        <v>323.94</v>
+      </c>
+      <c r="O38" s="8" t="n">
         <v>89.7</v>
       </c>
-      <c r="P37" s="9" t="n">
+      <c r="P38" s="9" t="n">
         <v>78.90000000000001</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>OWN-EB2-C1-ST</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>kaggle_fruits_fresh_rotten_all_frozen_efficientnet_b2</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>own_dataset</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="I39" s="9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>0.6573</v>
+      </c>
+      <c r="N39" s="9" t="n">
+        <v>343.62</v>
+      </c>
+      <c r="O39" s="9" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="P39" s="8" t="n">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -8817,7 +9259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8969,7 +9411,7 @@
         <v>0.993</v>
       </c>
       <c r="N2" s="9" t="n">
-        <v>623.8200000000001</v>
+        <v>332.17</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>69.90000000000001</v>
@@ -9027,7 +9469,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>469.04</v>
+        <v>331.42</v>
       </c>
       <c r="O3" s="9" t="n">
         <v>82</v>
@@ -9085,7 +9527,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>335.3</v>
+        <v>371.77</v>
       </c>
       <c r="O4" s="8" t="n">
         <v>65.59999999999999</v>
@@ -9143,7 +9585,7 @@
         <v>0.8741</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>362.15</v>
+        <v>256.86</v>
       </c>
       <c r="O5" s="9" t="n">
         <v>99.40000000000001</v>
@@ -9201,7 +9643,7 @@
         <v>0.8951</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>519.98</v>
+        <v>409.89</v>
       </c>
       <c r="O6" s="9" t="n">
         <v>95.5</v>
@@ -9259,7 +9701,7 @@
         <v>0.9301</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>329.88</v>
+        <v>348.16</v>
       </c>
       <c r="O7" s="9" t="n">
         <v>88.7</v>
@@ -9317,7 +9759,7 @@
         <v>0.9161</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>285.52</v>
+        <v>439.11</v>
       </c>
       <c r="O8" s="9" t="n">
         <v>77.09999999999999</v>
@@ -9375,7 +9817,7 @@
         <v>0.9441000000000001</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>291.59</v>
+        <v>444.53</v>
       </c>
       <c r="O9" s="9" t="n">
         <v>89.40000000000001</v>
@@ -9433,7 +9875,7 @@
         <v>0.9091</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>385.14</v>
+        <v>273.67</v>
       </c>
       <c r="O10" s="9" t="n">
         <v>92.09999999999999</v>
@@ -9491,7 +9933,7 @@
         <v>0.951</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>402.49</v>
+        <v>425.73</v>
       </c>
       <c r="O11" s="9" t="n">
         <v>91.90000000000001</v>
@@ -9549,7 +9991,7 @@
         <v>0.9441000000000001</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>399.7</v>
+        <v>428.54</v>
       </c>
       <c r="O12" s="9" t="n">
         <v>89.5</v>
@@ -9607,7 +10049,7 @@
         <v>0.9301</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>361.02</v>
+        <v>361.53</v>
       </c>
       <c r="O13" s="9" t="n">
         <v>80.7</v>
@@ -9622,12 +10064,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C1-ST</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fresh_stale_all_frozen_resnet18</t>
+          <t>kaggle_fresh_stale_all_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -9641,13 +10083,13 @@
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>83.2</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>11.8</v>
+        <v>13.8</v>
       </c>
       <c r="I14" s="8" t="n">
         <v>83.2</v>
@@ -9661,17 +10103,17 @@
       <c r="L14" s="9" t="n">
         <v>0.664</v>
       </c>
-      <c r="M14" s="8" t="n">
-        <v>0.8881</v>
+      <c r="M14" s="7" t="n">
+        <v>0.9441000000000001</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>474.84</v>
-      </c>
-      <c r="O14" s="9" t="n">
-        <v>87.90000000000001</v>
+        <v>502.89</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>71.40000000000001</v>
       </c>
       <c r="P14" s="7" t="n">
-        <v>93.90000000000001</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -9680,12 +10122,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-R18-C1-ST</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fresh_stale_all_head_frozen_resnet18</t>
+          <t>kaggle_fresh_stale_all_frozen_resnet18</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -9699,13 +10141,13 @@
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>83.2</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>14.8</v>
+        <v>11.8</v>
       </c>
       <c r="I15" s="8" t="n">
         <v>83.2</v>
@@ -9720,16 +10162,16 @@
         <v>0.664</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.8951</v>
+        <v>0.8881</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>368.93</v>
+        <v>476.71</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>76.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P15" s="7" t="n">
-        <v>95.7</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -9738,12 +10180,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C4-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_head_layer4_resnet18</t>
+          <t>kaggle_fresh_stale_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -9756,14 +10198,14 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F16" s="8" t="n">
-        <v>88.90000000000001</v>
+      <c r="F16" s="7" t="n">
+        <v>98</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>83.2</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>5.7</v>
+        <v>14.8</v>
       </c>
       <c r="I16" s="8" t="n">
         <v>83.2</v>
@@ -9778,16 +10220,16 @@
         <v>0.664</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.8741</v>
+        <v>0.8951</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>429.45</v>
+        <v>260.52</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>88.09999999999999</v>
-      </c>
-      <c r="P16" s="8" t="n">
-        <v>87.7</v>
+        <v>76.8</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>95.7</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -9796,12 +10238,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C1-ST</t>
+          <t>OWN-R18-C4-ST</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_frozen_efficientnet_b0</t>
+          <t>kaggle_fruits_quality_all_head_layer4_resnet18</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -9815,37 +10257,37 @@
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>84.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>2.2</v>
+        <v>83.2</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>5.7</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>82.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>83.3</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>84.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.669</v>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>0.951</v>
+        <v>0.664</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>0.8741</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>328.35</v>
+        <v>344.09</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>79</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>89.59999999999999</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -9854,12 +10296,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-EB0-C1-ST</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_head_frozen_resnet18</t>
+          <t>kaggle_fruits_quality_all_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -9873,13 +10315,13 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>86.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>82.5</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="I18" s="8" t="n">
         <v>82.90000000000001</v>
@@ -9893,17 +10335,17 @@
       <c r="L18" s="9" t="n">
         <v>0.669</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>0.8322000000000001</v>
+      <c r="M18" s="7" t="n">
+        <v>0.951</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>335.32</v>
+        <v>370.7</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>89.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="P18" s="8" t="n">
-        <v>89.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -9912,12 +10354,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_quality_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -9930,14 +10372,14 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F19" s="7" t="n">
-        <v>91.7</v>
+      <c r="F19" s="8" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>82.5</v>
       </c>
-      <c r="H19" s="8" t="n">
-        <v>9.199999999999999</v>
+      <c r="H19" s="7" t="n">
+        <v>3.6</v>
       </c>
       <c r="I19" s="8" t="n">
         <v>82.90000000000001</v>
@@ -9952,16 +10394,16 @@
         <v>0.669</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.8881</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>380.33</v>
+        <v>357.29</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>84.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P19" s="8" t="n">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -9970,12 +10412,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C3-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_head_frozen_efficientnet_b0</t>
+          <t>mendeley_fruits_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -9989,13 +10431,13 @@
         </is>
       </c>
       <c r="F20" s="7" t="n">
-        <v>98.7</v>
+        <v>91.7</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>82.5</v>
       </c>
-      <c r="H20" s="9" t="n">
-        <v>16.2</v>
+      <c r="H20" s="8" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>82.90000000000001</v>
@@ -10009,17 +10451,17 @@
       <c r="L20" s="9" t="n">
         <v>0.669</v>
       </c>
-      <c r="M20" s="7" t="n">
-        <v>0.958</v>
+      <c r="M20" s="8" t="n">
+        <v>0.8881</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>324.19</v>
+        <v>407.64</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="P20" s="7" t="n">
-        <v>98.2</v>
+        <v>84.59999999999999</v>
+      </c>
+      <c r="P20" s="8" t="n">
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -10028,12 +10470,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C3-ST</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_frozen_resnet18</t>
+          <t>mendeley_lemon_varieties_all_head_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -10047,37 +10489,37 @@
         </is>
       </c>
       <c r="F21" s="7" t="n">
-        <v>97.7</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>79.40000000000001</v>
+        <v>98.7</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>82.5</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="K21" s="9" t="n">
-        <v>79.2</v>
+        <v>16.2</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>84.40000000000001</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="M21" s="8" t="n">
-        <v>0.8462</v>
+        <v>0.669</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>0.958</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>350.7</v>
+        <v>330.89</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>85</v>
+        <v>91.5</v>
       </c>
       <c r="P21" s="7" t="n">
-        <v>96.2</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -10086,12 +10528,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-R18-C1-ST</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_fresh_rotten_all_frozen_resnet18</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -10104,14 +10546,14 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F22" s="8" t="n">
-        <v>86.09999999999999</v>
+      <c r="F22" s="7" t="n">
+        <v>97.7</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="H22" s="8" t="n">
-        <v>6.7</v>
+      <c r="H22" s="9" t="n">
+        <v>18.3</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>79.09999999999999</v>
@@ -10125,17 +10567,17 @@
       <c r="L22" s="9" t="n">
         <v>0.585</v>
       </c>
-      <c r="M22" s="7" t="n">
-        <v>0.9091</v>
+      <c r="M22" s="8" t="n">
+        <v>0.8462</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>332.3</v>
-      </c>
-      <c r="O22" s="8" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>89.09999999999999</v>
+        <v>343.39</v>
+      </c>
+      <c r="O22" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="P22" s="7" t="n">
+        <v>96.2</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -10144,12 +10586,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C2-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fresh_stale_all_layer4_resnet18</t>
+          <t>kaggle_fruits_quality_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -10162,38 +10604,38 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F23" s="7" t="n">
-        <v>98.90000000000001</v>
+      <c r="F23" s="8" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>20.2</v>
+        <v>79.40000000000001</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>6.7</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>78.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="J23" s="9" t="n">
         <v>79.2</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="M23" s="8" t="n">
-        <v>0.8811</v>
+        <v>0.585</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>0.9091</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>396.21</v>
-      </c>
-      <c r="O23" s="9" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="P23" s="7" t="n">
-        <v>96</v>
+        <v>367.21</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="P23" s="8" t="n">
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -10202,12 +10644,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-R18-C2-ST</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_head_frozen_resnet18</t>
+          <t>kaggle_fresh_stale_all_layer4_resnet18</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -10221,13 +10663,13 @@
         </is>
       </c>
       <c r="F24" s="7" t="n">
-        <v>99.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>78.7</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>20.7</v>
+        <v>20.2</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>78.8</v>
@@ -10242,16 +10684,16 @@
         <v>0.58</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8811</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>519.6</v>
+        <v>308.36</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>89.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="P24" s="7" t="n">
-        <v>97.09999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -10260,12 +10702,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C4-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_head_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_fresh_rotten_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -10278,14 +10720,14 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F25" s="8" t="n">
-        <v>86.09999999999999</v>
+      <c r="F25" s="7" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>78.7</v>
       </c>
-      <c r="H25" s="8" t="n">
-        <v>7.4</v>
+      <c r="H25" s="9" t="n">
+        <v>20.7</v>
       </c>
       <c r="I25" s="9" t="n">
         <v>78.8</v>
@@ -10300,16 +10742,16 @@
         <v>0.58</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.8671</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>382.52</v>
+        <v>421.72</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>84</v>
-      </c>
-      <c r="P25" s="8" t="n">
         <v>89.40000000000001</v>
+      </c>
+      <c r="P25" s="7" t="n">
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -10318,12 +10760,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-EB0-C4-ST</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_head_frozen_resnet18</t>
+          <t>kaggle_fruits_quality_all_head_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -10336,14 +10778,14 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F26" s="7" t="n">
-        <v>95.2</v>
+      <c r="F26" s="8" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>78.7</v>
       </c>
-      <c r="H26" s="9" t="n">
-        <v>16.5</v>
+      <c r="H26" s="8" t="n">
+        <v>7.4</v>
       </c>
       <c r="I26" s="9" t="n">
         <v>78.8</v>
@@ -10361,13 +10803,13 @@
         <v>0.8671</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>405.4</v>
+        <v>352.2</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="P26" s="7" t="n">
-        <v>93.5</v>
+        <v>84</v>
+      </c>
+      <c r="P26" s="8" t="n">
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -10376,12 +10818,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C4-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_head_layer4_efficientnet_b0</t>
+          <t>mendeley_fruits_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -10395,13 +10837,13 @@
         </is>
       </c>
       <c r="F27" s="7" t="n">
-        <v>95.8</v>
+        <v>95.2</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>78.7</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>17.1</v>
+        <v>16.5</v>
       </c>
       <c r="I27" s="9" t="n">
         <v>78.8</v>
@@ -10419,13 +10861,13 @@
         <v>0.8671</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>413.3</v>
+        <v>276.83</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="P27" s="8" t="n">
-        <v>86.59999999999999</v>
+        <v>85.40000000000001</v>
+      </c>
+      <c r="P27" s="7" t="n">
+        <v>93.5</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -10434,12 +10876,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C4-ST</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_frozen_resnet18</t>
+          <t>mendeley_fruits_all_head_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -10453,37 +10895,37 @@
         </is>
       </c>
       <c r="F28" s="7" t="n">
-        <v>94.3</v>
+        <v>95.8</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>78</v>
+        <v>78.7</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>16.3</v>
+        <v>17.1</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>78.2</v>
+        <v>78.8</v>
       </c>
       <c r="J28" s="9" t="n">
         <v>79.2</v>
       </c>
-      <c r="K28" s="8" t="n">
-        <v>81.2</v>
+      <c r="K28" s="9" t="n">
+        <v>79.3</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.591</v>
+        <v>0.58</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>0.8951</v>
+        <v>0.8671</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>330.85</v>
+        <v>294.63</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="P28" s="7" t="n">
-        <v>92.90000000000001</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -10492,12 +10934,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C1-ST</t>
+          <t>OWN-R18-C1-ST</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_frozen_efficientnet_b0</t>
+          <t>mendeley_fruits_all_frozen_resnet18</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -10511,13 +10953,13 @@
         </is>
       </c>
       <c r="F29" s="7" t="n">
-        <v>96.7</v>
+        <v>94.3</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>78</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>18.7</v>
+        <v>16.3</v>
       </c>
       <c r="I29" s="9" t="n">
         <v>78.2</v>
@@ -10531,17 +10973,17 @@
       <c r="L29" s="9" t="n">
         <v>0.591</v>
       </c>
-      <c r="M29" s="7" t="n">
-        <v>0.972</v>
+      <c r="M29" s="8" t="n">
+        <v>0.8951</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>370.88</v>
+        <v>417.26</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>76.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="P29" s="7" t="n">
-        <v>97.5</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -10550,12 +10992,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-EB0-C1-ST</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_layer4_efficientnet_b0</t>
+          <t>mendeley_lemon_varieties_all_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -10569,37 +11011,37 @@
         </is>
       </c>
       <c r="F30" s="7" t="n">
-        <v>94.7</v>
+        <v>96.7</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>76.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>17.8</v>
+        <v>18.7</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>74.3</v>
+        <v>78.2</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>75</v>
+        <v>79.2</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>82.3</v>
+        <v>81.2</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="M30" s="8" t="n">
-        <v>0.8881</v>
+        <v>0.591</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>0.972</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>395.42</v>
-      </c>
-      <c r="O30" s="8" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="P30" s="8" t="n">
-        <v>83.5</v>
+        <v>387.76</v>
+      </c>
+      <c r="O30" s="9" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="P30" s="7" t="n">
+        <v>97.5</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -10608,12 +11050,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C2-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_layer4_resnet18</t>
+          <t>mendeley_lemon_varieties_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -10627,37 +11069,37 @@
         </is>
       </c>
       <c r="F31" s="7" t="n">
-        <v>99.8</v>
+        <v>94.7</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>75.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>24.3</v>
+        <v>17.8</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>75</v>
+        <v>74.3</v>
       </c>
       <c r="J31" s="9" t="n">
         <v>75</v>
       </c>
-      <c r="K31" s="9" t="n">
-        <v>75.5</v>
+      <c r="K31" s="8" t="n">
+        <v>82.3</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.51</v>
+        <v>0.59</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.8252</v>
+        <v>0.8881</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>339.63</v>
-      </c>
-      <c r="O31" s="9" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="P31" s="7" t="n">
-        <v>96.7</v>
+        <v>350.65</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="P31" s="8" t="n">
+        <v>83.5</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -10666,12 +11108,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C4-ST</t>
+          <t>OWN-R18-C2-ST</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_head_layer4_resnet18</t>
+          <t>kaggle_fruits_fresh_rotten_all_layer4_resnet18</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -10688,34 +11130,34 @@
         <v>99.8</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>71</v>
+        <v>75.5</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>28.8</v>
+        <v>24.3</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>70.8</v>
+        <v>75</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>70.8</v>
+        <v>75</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>70.8</v>
+        <v>75.5</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="M32" s="9" t="n">
-        <v>0.7902</v>
+        <v>0.51</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>0.8252</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>463.91</v>
+        <v>274.91</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>83.8</v>
+        <v>90.2</v>
       </c>
       <c r="P32" s="7" t="n">
-        <v>92.3</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -10724,12 +11166,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-R18-C4-ST</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_head_frozen_resnet18</t>
+          <t>kaggle_fruits_fresh_rotten_all_head_layer4_resnet18</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -10743,13 +11185,13 @@
         </is>
       </c>
       <c r="F33" s="7" t="n">
-        <v>96.2</v>
+        <v>99.8</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>71</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>25.2</v>
+        <v>28.8</v>
       </c>
       <c r="I33" s="9" t="n">
         <v>70.8</v>
@@ -10763,17 +11205,17 @@
       <c r="L33" s="9" t="n">
         <v>0.418</v>
       </c>
-      <c r="M33" s="8" t="n">
-        <v>0.8391999999999999</v>
+      <c r="M33" s="9" t="n">
+        <v>0.7902</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>340.66</v>
-      </c>
-      <c r="O33" s="8" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="P33" s="8" t="n">
-        <v>87.7</v>
+        <v>313.74</v>
+      </c>
+      <c r="O33" s="9" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="P33" s="7" t="n">
+        <v>92.3</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -10782,12 +11224,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C4-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_head_layer4_efficientnet_b0</t>
+          <t>mendeley_lemon_varieties_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -10801,37 +11243,37 @@
         </is>
       </c>
       <c r="F34" s="7" t="n">
-        <v>99.7</v>
+        <v>96.2</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>65.7</v>
+        <v>71</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>34</v>
+        <v>25.2</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>65.7</v>
+        <v>70.8</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>66.7</v>
+        <v>70.8</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>66.7</v>
+        <v>70.8</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="M34" s="9" t="n">
-        <v>0.7343</v>
+        <v>0.418</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>0.8391999999999999</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>540.1900000000001</v>
-      </c>
-      <c r="O34" s="9" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="P34" s="7" t="n">
-        <v>91.8</v>
+        <v>354.54</v>
+      </c>
+      <c r="O34" s="8" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="P34" s="8" t="n">
+        <v>87.7</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -10840,12 +11282,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-EB0-C4-ST</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_fresh_rotten_all_head_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -10859,13 +11301,13 @@
         </is>
       </c>
       <c r="F35" s="7" t="n">
-        <v>98.8</v>
+        <v>99.7</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>65.7</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>33.1</v>
+        <v>34</v>
       </c>
       <c r="I35" s="9" t="n">
         <v>65.7</v>
@@ -10880,16 +11322,16 @@
         <v>0.324</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.7762</v>
+        <v>0.7343</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>357.03</v>
+        <v>413.66</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>82.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="P35" s="7" t="n">
-        <v>90.90000000000001</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -10898,12 +11340,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_frozen_resnet18</t>
+          <t>kaggle_fruits_fresh_rotten_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -10917,37 +11359,37 @@
         </is>
       </c>
       <c r="F36" s="7" t="n">
-        <v>96.2</v>
+        <v>98.8</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>63.6</v>
+        <v>65.7</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>32.6</v>
+        <v>33.1</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>59.7</v>
+        <v>65.7</v>
       </c>
       <c r="J36" s="9" t="n">
         <v>66.7</v>
       </c>
-      <c r="K36" s="8" t="n">
-        <v>81</v>
+      <c r="K36" s="9" t="n">
+        <v>66.7</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>0.8671</v>
+        <v>0.324</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>0.7762</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>309.16</v>
+        <v>260.97</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="P36" s="8" t="n">
-        <v>89.7</v>
+        <v>82.7</v>
+      </c>
+      <c r="P36" s="7" t="n">
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -10961,50 +11403,166 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
+          <t>mendeley_lemon_varieties_all_frozen_resnet18</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>own_dataset</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="I37" s="9" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="K37" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>0.8671</v>
+      </c>
+      <c r="N37" s="9" t="n">
+        <v>323.94</v>
+      </c>
+      <c r="O37" s="9" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="P37" s="8" t="n">
+        <v>89.7</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>OWN-EB2-C1-ST</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>kaggle_fruits_fresh_rotten_all_frozen_efficientnet_b2</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>own_dataset</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="I38" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="L38" s="9" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="M38" s="9" t="n">
+        <v>0.6573</v>
+      </c>
+      <c r="N38" s="9" t="n">
+        <v>343.62</v>
+      </c>
+      <c r="O38" s="8" t="n">
+        <v>74</v>
+      </c>
+      <c r="P38" s="9" t="n">
+        <v>79.90000000000001</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>OWN-R18-C1-ST</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
           <t>kaggle_fruits_quality_all_frozen_resnet18</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>own_dataset</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="n">
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>own_dataset</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="G37" s="9" t="n">
+      <c r="G39" s="9" t="n">
         <v>59.4</v>
       </c>
-      <c r="H37" s="9" t="n">
+      <c r="H39" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="I37" s="9" t="n">
+      <c r="I39" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="J37" s="9" t="n">
+      <c r="J39" s="9" t="n">
         <v>58.3</v>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K39" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L39" s="9" t="n">
         <v>0.194</v>
       </c>
-      <c r="M37" s="8" t="n">
+      <c r="M39" s="8" t="n">
         <v>0.8531</v>
       </c>
-      <c r="N37" s="9" t="n">
-        <v>352.47</v>
-      </c>
-      <c r="O37" s="7" t="n">
+      <c r="N39" s="9" t="n">
+        <v>348.08</v>
+      </c>
+      <c r="O39" s="7" t="n">
         <v>57.6</v>
       </c>
-      <c r="P37" s="9" t="n">
+      <c r="P39" s="9" t="n">
         <v>77.09999999999999</v>
       </c>
     </row>
@@ -11019,7 +11577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11171,7 +11729,7 @@
         <v>0.993</v>
       </c>
       <c r="N2" s="9" t="n">
-        <v>623.8200000000001</v>
+        <v>332.17</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>87.09999999999999</v>
@@ -11229,7 +11787,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>469.04</v>
+        <v>331.42</v>
       </c>
       <c r="O3" s="7" t="n">
         <v>91.8</v>
@@ -11287,7 +11845,7 @@
         <v>0.8741</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>362.15</v>
+        <v>256.86</v>
       </c>
       <c r="O4" s="7" t="n">
         <v>96.59999999999999</v>
@@ -11345,7 +11903,7 @@
         <v>0.9301</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>361.02</v>
+        <v>361.53</v>
       </c>
       <c r="O5" s="7" t="n">
         <v>93.09999999999999</v>
@@ -11403,7 +11961,7 @@
         <v>0.8951</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>519.98</v>
+        <v>409.89</v>
       </c>
       <c r="O6" s="7" t="n">
         <v>92</v>
@@ -11461,7 +12019,7 @@
         <v>0.9301</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>329.88</v>
+        <v>348.16</v>
       </c>
       <c r="O7" s="8" t="n">
         <v>89.7</v>
@@ -11519,7 +12077,7 @@
         <v>0.9161</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>285.52</v>
+        <v>439.11</v>
       </c>
       <c r="O8" s="8" t="n">
         <v>86.3</v>
@@ -11577,7 +12135,7 @@
         <v>0.9441000000000001</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>291.59</v>
+        <v>444.53</v>
       </c>
       <c r="O9" s="7" t="n">
         <v>93.90000000000001</v>
@@ -11635,7 +12193,7 @@
         <v>0.9091</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>385.14</v>
+        <v>273.67</v>
       </c>
       <c r="O10" s="7" t="n">
         <v>97.3</v>
@@ -11693,7 +12251,7 @@
         <v>0.951</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>402.49</v>
+        <v>425.73</v>
       </c>
       <c r="O11" s="7" t="n">
         <v>95.3</v>
@@ -11751,7 +12309,7 @@
         <v>0.9441000000000001</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>399.7</v>
+        <v>428.54</v>
       </c>
       <c r="O12" s="7" t="n">
         <v>94.90000000000001</v>
@@ -11809,7 +12367,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>335.3</v>
+        <v>371.77</v>
       </c>
       <c r="O13" s="8" t="n">
         <v>88.5</v>
@@ -11824,12 +12382,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C1-ST</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fresh_stale_all_frozen_resnet18</t>
+          <t>kaggle_fresh_stale_all_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -11843,13 +12401,13 @@
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>83.3</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>11.7</v>
+        <v>13.7</v>
       </c>
       <c r="I14" s="8" t="n">
         <v>83.2</v>
@@ -11863,17 +12421,17 @@
       <c r="L14" s="9" t="n">
         <v>0.664</v>
       </c>
-      <c r="M14" s="8" t="n">
-        <v>0.8881</v>
+      <c r="M14" s="7" t="n">
+        <v>0.9441000000000001</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>474.84</v>
+        <v>502.89</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="P14" s="9" t="n">
-        <v>87.90000000000001</v>
+        <v>91.7</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -11882,12 +12440,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-R18-C1-ST</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fresh_stale_all_head_frozen_resnet18</t>
+          <t>kaggle_fresh_stale_all_frozen_resnet18</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -11901,13 +12459,13 @@
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>83.3</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>14.7</v>
+        <v>11.7</v>
       </c>
       <c r="I15" s="8" t="n">
         <v>83.2</v>
@@ -11922,16 +12480,16 @@
         <v>0.664</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0.8951</v>
+        <v>0.8881</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>368.93</v>
+        <v>476.71</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>95.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>76.8</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -11940,12 +12498,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C1-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_frozen_efficientnet_b0</t>
+          <t>kaggle_fresh_stale_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -11958,38 +12516,38 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F16" s="8" t="n">
-        <v>84.7</v>
+      <c r="F16" s="7" t="n">
+        <v>98</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>83.3</v>
       </c>
-      <c r="H16" s="7" t="n">
-        <v>1.4</v>
+      <c r="H16" s="8" t="n">
+        <v>14.7</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>82.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>84.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>82.5</v>
+        <v>83.2</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.669</v>
-      </c>
-      <c r="M16" s="7" t="n">
-        <v>0.951</v>
+        <v>0.664</v>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>0.8951</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>328.35</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>89.59999999999999</v>
+        <v>260.52</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>95.7</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>79</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -11998,12 +12556,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-EB0-C1-ST</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_head_frozen_resnet18</t>
+          <t>kaggle_fruits_quality_all_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -12017,13 +12575,13 @@
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>86.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>83.3</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="I17" s="8" t="n">
         <v>82.90000000000001</v>
@@ -12037,17 +12595,17 @@
       <c r="L17" s="9" t="n">
         <v>0.669</v>
       </c>
-      <c r="M17" s="8" t="n">
-        <v>0.8322000000000001</v>
+      <c r="M17" s="7" t="n">
+        <v>0.951</v>
       </c>
       <c r="N17" s="9" t="n">
-        <v>335.32</v>
+        <v>370.7</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>89.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>89.09999999999999</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -12056,12 +12614,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C4-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_head_layer4_resnet18</t>
+          <t>kaggle_fruits_quality_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -12075,37 +12633,37 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>88.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>83.3</v>
       </c>
-      <c r="H18" s="8" t="n">
-        <v>5.6</v>
+      <c r="H18" s="7" t="n">
+        <v>2.8</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>83.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>83.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>83.2</v>
+        <v>82.5</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.664</v>
+        <v>0.669</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>0.8741</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>429.45</v>
+        <v>357.29</v>
       </c>
       <c r="O18" s="8" t="n">
-        <v>87.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>88.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -12114,12 +12672,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-R18-C4-ST</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_quality_all_head_layer4_resnet18</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -12132,38 +12690,38 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F19" s="7" t="n">
-        <v>91.5</v>
+      <c r="F19" s="8" t="n">
+        <v>88.90000000000001</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>83.3</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>82.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>84.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>82.5</v>
+        <v>83.2</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.669</v>
+        <v>0.664</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>0.8881</v>
+        <v>0.8741</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>380.33</v>
+        <v>344.09</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>88.59999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="P19" s="9" t="n">
-        <v>84.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -12172,12 +12730,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C3-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_head_frozen_efficientnet_b0</t>
+          <t>mendeley_fruits_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -12191,13 +12749,13 @@
         </is>
       </c>
       <c r="F20" s="7" t="n">
-        <v>98.7</v>
+        <v>91.5</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>83.3</v>
       </c>
-      <c r="H20" s="9" t="n">
-        <v>15.4</v>
+      <c r="H20" s="8" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>82.90000000000001</v>
@@ -12211,17 +12769,17 @@
       <c r="L20" s="9" t="n">
         <v>0.669</v>
       </c>
-      <c r="M20" s="7" t="n">
-        <v>0.958</v>
+      <c r="M20" s="8" t="n">
+        <v>0.8881</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>324.19</v>
-      </c>
-      <c r="O20" s="7" t="n">
-        <v>98.2</v>
+        <v>407.64</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>88.59999999999999</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>91.5</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -12230,12 +12788,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C2-ST</t>
+          <t>OWN-EB0-C3-ST</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fresh_stale_all_layer4_resnet18</t>
+          <t>mendeley_lemon_varieties_all_head_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -12249,37 +12807,37 @@
         </is>
       </c>
       <c r="F21" s="7" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>79.2</v>
+        <v>98.7</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>83.3</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="K21" s="9" t="n">
-        <v>78.7</v>
+        <v>15.4</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>82.5</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="M21" s="8" t="n">
-        <v>0.8811</v>
+        <v>0.669</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>0.958</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>396.21</v>
+        <v>330.89</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>96</v>
+        <v>98.2</v>
       </c>
       <c r="P21" s="9" t="n">
-        <v>81.2</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -12288,12 +12846,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-R18-C2-ST</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_frozen_resnet18</t>
+          <t>kaggle_fresh_stale_all_layer4_resnet18</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -12307,37 +12865,37 @@
         </is>
       </c>
       <c r="F22" s="7" t="n">
-        <v>97.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>79.2</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>18.4</v>
+        <v>19.7</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>79.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>79.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.585</v>
+        <v>0.58</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>0.8462</v>
+        <v>0.8811</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>350.7</v>
+        <v>308.36</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>96.2</v>
+        <v>96</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>85</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -12346,12 +12904,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-R18-C1-ST</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_head_frozen_resnet18</t>
+          <t>kaggle_fruits_fresh_rotten_all_frozen_resnet18</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -12365,37 +12923,37 @@
         </is>
       </c>
       <c r="F23" s="7" t="n">
-        <v>99.40000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>79.2</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>20.2</v>
+        <v>18.4</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>78.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>78.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.58</v>
+        <v>0.585</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8462</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>519.6</v>
+        <v>343.39</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>97.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="P23" s="9" t="n">
-        <v>89.40000000000001</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -12404,12 +12962,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C4-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_head_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_fresh_rotten_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -12422,14 +12980,14 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F24" s="8" t="n">
-        <v>86.09999999999999</v>
+      <c r="F24" s="7" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>79.2</v>
       </c>
-      <c r="H24" s="8" t="n">
-        <v>6.9</v>
+      <c r="H24" s="9" t="n">
+        <v>20.2</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>78.8</v>
@@ -12444,16 +13002,16 @@
         <v>0.58</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.8671</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>382.52</v>
-      </c>
-      <c r="O24" s="8" t="n">
+        <v>421.72</v>
+      </c>
+      <c r="O24" s="7" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="P24" s="9" t="n">
         <v>89.40000000000001</v>
-      </c>
-      <c r="P24" s="9" t="n">
-        <v>84</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -12462,12 +13020,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-EB0-C4-ST</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_quality_all_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_quality_all_head_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -12490,28 +13048,28 @@
         <v>6.9</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>79.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>79.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="M25" s="7" t="n">
-        <v>0.9091</v>
+        <v>0.58</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>0.8671</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>332.3</v>
+        <v>352.2</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="P25" s="8" t="n">
-        <v>73.8</v>
+        <v>89.40000000000001</v>
+      </c>
+      <c r="P25" s="9" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -12520,12 +13078,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_frozen_resnet18</t>
+          <t>kaggle_fruits_quality_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -12538,38 +13096,38 @@
           <t>state</t>
         </is>
       </c>
-      <c r="F26" s="7" t="n">
-        <v>94.3</v>
+      <c r="F26" s="8" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>79.2</v>
       </c>
-      <c r="H26" s="9" t="n">
-        <v>15.1</v>
+      <c r="H26" s="8" t="n">
+        <v>6.9</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="J26" s="8" t="n">
-        <v>81.2</v>
+        <v>79.09999999999999</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>79.2</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>78</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="M26" s="8" t="n">
-        <v>0.8951</v>
+        <v>0.585</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>0.9091</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>330.85</v>
-      </c>
-      <c r="O26" s="7" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="P26" s="9" t="n">
-        <v>75.5</v>
+        <v>367.21</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="P26" s="8" t="n">
+        <v>73.8</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -12578,12 +13136,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-R18-C1-ST</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_head_frozen_resnet18</t>
+          <t>mendeley_fruits_all_frozen_resnet18</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -12597,37 +13155,37 @@
         </is>
       </c>
       <c r="F27" s="7" t="n">
-        <v>95.2</v>
+        <v>94.3</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>79.2</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>16</v>
+        <v>15.1</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="J27" s="9" t="n">
-        <v>79.3</v>
+        <v>78.2</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>81.2</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>78.7</v>
+        <v>78</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.58</v>
+        <v>0.591</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0.8671</v>
+        <v>0.8951</v>
       </c>
       <c r="N27" s="9" t="n">
-        <v>405.4</v>
+        <v>417.26</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>93.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P27" s="9" t="n">
-        <v>85.40000000000001</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -12636,12 +13194,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C4-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>mendeley_fruits_all_head_layer4_efficientnet_b0</t>
+          <t>mendeley_fruits_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -12655,13 +13213,13 @@
         </is>
       </c>
       <c r="F28" s="7" t="n">
-        <v>95.8</v>
+        <v>95.2</v>
       </c>
       <c r="G28" s="9" t="n">
         <v>79.2</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>16.6</v>
+        <v>16</v>
       </c>
       <c r="I28" s="9" t="n">
         <v>78.8</v>
@@ -12679,13 +13237,13 @@
         <v>0.8671</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>413.3</v>
-      </c>
-      <c r="O28" s="8" t="n">
-        <v>86.59999999999999</v>
+        <v>276.83</v>
+      </c>
+      <c r="O28" s="7" t="n">
+        <v>93.5</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>75.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -12694,12 +13252,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C1-ST</t>
+          <t>OWN-EB0-C4-ST</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_frozen_efficientnet_b0</t>
+          <t>mendeley_fruits_all_head_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -12713,37 +13271,37 @@
         </is>
       </c>
       <c r="F29" s="7" t="n">
-        <v>96.7</v>
+        <v>95.8</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>79.2</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>17.5</v>
+        <v>16.6</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="J29" s="8" t="n">
-        <v>81.2</v>
+        <v>78.8</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>79.3</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>78</v>
+        <v>78.7</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="M29" s="7" t="n">
-        <v>0.972</v>
+        <v>0.58</v>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>0.8671</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>370.88</v>
-      </c>
-      <c r="O29" s="7" t="n">
-        <v>97.5</v>
+        <v>294.63</v>
+      </c>
+      <c r="O29" s="8" t="n">
+        <v>86.59999999999999</v>
       </c>
       <c r="P29" s="9" t="n">
-        <v>76.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -12752,12 +13310,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C2-ST</t>
+          <t>OWN-EB0-C1-ST</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_layer4_resnet18</t>
+          <t>mendeley_lemon_varieties_all_frozen_efficientnet_b0</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -12771,37 +13329,37 @@
         </is>
       </c>
       <c r="F30" s="7" t="n">
-        <v>99.8</v>
+        <v>96.7</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>75</v>
+        <v>79.2</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>24.8</v>
+        <v>17.5</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>75</v>
-      </c>
-      <c r="J30" s="9" t="n">
-        <v>75.5</v>
+        <v>78.2</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>81.2</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>75.5</v>
+        <v>78</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="M30" s="8" t="n">
-        <v>0.8252</v>
+        <v>0.591</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>0.972</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>339.63</v>
+        <v>387.76</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>96.7</v>
+        <v>97.5</v>
       </c>
       <c r="P30" s="9" t="n">
-        <v>90.2</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -12810,12 +13368,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-R18-C2-ST</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_fresh_rotten_all_layer4_resnet18</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -12829,37 +13387,37 @@
         </is>
       </c>
       <c r="F31" s="7" t="n">
-        <v>94.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>75</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>19.6</v>
+        <v>24.8</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="J31" s="8" t="n">
-        <v>82.3</v>
+        <v>75</v>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>75.5</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>76.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0.8881</v>
+        <v>0.8252</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>395.42</v>
-      </c>
-      <c r="O31" s="8" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="P31" s="8" t="n">
-        <v>70.09999999999999</v>
+        <v>274.91</v>
+      </c>
+      <c r="O31" s="7" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="P31" s="9" t="n">
+        <v>90.2</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -12868,12 +13426,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C4-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_head_layer4_resnet18</t>
+          <t>mendeley_lemon_varieties_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -12887,37 +13445,37 @@
         </is>
       </c>
       <c r="F32" s="7" t="n">
-        <v>99.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>70.8</v>
+        <v>75</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>29</v>
+        <v>19.6</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>70.8</v>
+        <v>74.3</v>
+      </c>
+      <c r="J32" s="8" t="n">
+        <v>82.3</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>71</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="M32" s="9" t="n">
-        <v>0.7902</v>
+        <v>0.59</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>0.8881</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>463.91</v>
-      </c>
-      <c r="O32" s="7" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="P32" s="9" t="n">
-        <v>83.8</v>
+        <v>350.65</v>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="P32" s="8" t="n">
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -12926,12 +13484,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C3-ST</t>
+          <t>OWN-R18-C4-ST</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_head_frozen_resnet18</t>
+          <t>kaggle_fruits_fresh_rotten_all_head_layer4_resnet18</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -12945,13 +13503,13 @@
         </is>
       </c>
       <c r="F33" s="7" t="n">
-        <v>96.2</v>
+        <v>99.8</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>70.8</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>25.4</v>
+        <v>29</v>
       </c>
       <c r="I33" s="9" t="n">
         <v>70.8</v>
@@ -12965,17 +13523,17 @@
       <c r="L33" s="9" t="n">
         <v>0.418</v>
       </c>
-      <c r="M33" s="8" t="n">
-        <v>0.8391999999999999</v>
+      <c r="M33" s="9" t="n">
+        <v>0.7902</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>340.66</v>
-      </c>
-      <c r="O33" s="8" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="P33" s="8" t="n">
-        <v>72.09999999999999</v>
+        <v>313.74</v>
+      </c>
+      <c r="O33" s="7" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="P33" s="9" t="n">
+        <v>83.8</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -12984,12 +13542,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C4-ST</t>
+          <t>OWN-R18-C3-ST</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_head_layer4_efficientnet_b0</t>
+          <t>mendeley_lemon_varieties_all_head_frozen_resnet18</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -13003,37 +13561,37 @@
         </is>
       </c>
       <c r="F34" s="7" t="n">
-        <v>99.7</v>
+        <v>96.2</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>66.7</v>
+        <v>70.8</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>33</v>
+        <v>25.4</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>65.7</v>
+        <v>70.8</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>66.7</v>
+        <v>70.8</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>65.7</v>
+        <v>71</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="M34" s="9" t="n">
-        <v>0.7343</v>
+        <v>0.418</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>0.8391999999999999</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>540.1900000000001</v>
-      </c>
-      <c r="O34" s="7" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="P34" s="9" t="n">
-        <v>84.59999999999999</v>
+        <v>354.54</v>
+      </c>
+      <c r="O34" s="8" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="P34" s="8" t="n">
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -13042,12 +13600,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>OWN-EB0-C2-ST</t>
+          <t>OWN-EB0-C4-ST</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>kaggle_fruits_fresh_rotten_all_layer4_efficientnet_b0</t>
+          <t>kaggle_fruits_fresh_rotten_all_head_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -13061,13 +13619,13 @@
         </is>
       </c>
       <c r="F35" s="7" t="n">
-        <v>98.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>66.7</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>31.9</v>
+        <v>33</v>
       </c>
       <c r="I35" s="9" t="n">
         <v>65.7</v>
@@ -13082,16 +13640,16 @@
         <v>0.324</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.7762</v>
+        <v>0.7343</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>357.03</v>
+        <v>413.66</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>90.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="P35" s="9" t="n">
-        <v>82.7</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -13100,12 +13658,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>OWN-R18-C1-ST</t>
+          <t>OWN-EB0-C2-ST</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>mendeley_lemon_varieties_all_frozen_resnet18</t>
+          <t>kaggle_fruits_fresh_rotten_all_layer4_efficientnet_b0</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -13119,37 +13677,37 @@
         </is>
       </c>
       <c r="F36" s="7" t="n">
-        <v>96.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>66.7</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>29.5</v>
+        <v>31.9</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="J36" s="8" t="n">
-        <v>81</v>
+        <v>65.7</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>66.7</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>63.6</v>
+        <v>65.7</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>0.8671</v>
+        <v>0.324</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>0.7762</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>309.16</v>
-      </c>
-      <c r="O36" s="8" t="n">
-        <v>89.7</v>
+        <v>260.97</v>
+      </c>
+      <c r="O36" s="7" t="n">
+        <v>90.90000000000001</v>
       </c>
       <c r="P36" s="9" t="n">
-        <v>78.90000000000001</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -13163,50 +13721,166 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
+          <t>mendeley_lemon_varieties_all_frozen_resnet18</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>own_dataset</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="I37" s="9" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>0.8671</v>
+      </c>
+      <c r="N37" s="9" t="n">
+        <v>323.94</v>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="P37" s="9" t="n">
+        <v>78.90000000000001</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>OWN-EB2-C1-ST</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>kaggle_fruits_fresh_rotten_all_frozen_efficientnet_b2</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>own_dataset</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="I38" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="L38" s="9" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="M38" s="9" t="n">
+        <v>0.6573</v>
+      </c>
+      <c r="N38" s="9" t="n">
+        <v>343.62</v>
+      </c>
+      <c r="O38" s="9" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="P38" s="8" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>OWN-R18-C1-ST</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
           <t>kaggle_fruits_quality_all_frozen_resnet18</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>own_dataset</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="n">
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>own_dataset</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="G37" s="9" t="n">
+      <c r="G39" s="9" t="n">
         <v>58.3</v>
       </c>
-      <c r="H37" s="9" t="n">
+      <c r="H39" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="I37" s="9" t="n">
+      <c r="I39" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="J37" s="9" t="n">
+      <c r="J39" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K39" s="9" t="n">
         <v>59.4</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L39" s="9" t="n">
         <v>0.194</v>
       </c>
-      <c r="M37" s="8" t="n">
+      <c r="M39" s="8" t="n">
         <v>0.8531</v>
       </c>
-      <c r="N37" s="9" t="n">
-        <v>352.47</v>
-      </c>
-      <c r="O37" s="9" t="n">
+      <c r="N39" s="9" t="n">
+        <v>348.08</v>
+      </c>
+      <c r="O39" s="9" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="P37" s="7" t="n">
+      <c r="P39" s="7" t="n">
         <v>57.6</v>
       </c>
     </row>
